--- a/Resultados_Caso2.xlsx
+++ b/Resultados_Caso2.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{287AE04D-53B6-CF4D-91DB-2B4F246BABA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="22">
   <si>
     <t>Resultados de la simulación (81 escenarios)</t>
   </si>
@@ -101,13 +101,17 @@
   <si>
     <t>Página (B):</t>
   </si>
+  <si>
+    <t>Tiempo total (s)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000%"/>
+    <numFmt numFmtId="165" formatCode="0.000000"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -266,102 +270,98 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -373,7 +373,7 @@
     <xf numFmtId="3" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -391,7 +391,10 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5770,7 +5773,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:K85"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="11.6640625" customWidth="1"/>
@@ -5782,2806 +5785,3134 @@
     <col min="8" max="8" width="14.1640625" customWidth="1"/>
     <col min="9" max="9" width="15" customWidth="1"/>
     <col min="10" max="10" width="14.1640625" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="6" t="s">
+    <row r="4" spans="1:11" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="7">
+      <c r="K4" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="6">
         <v>1</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="6">
         <v>64</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="6">
         <v>4</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="6">
         <v>4</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="3">
         <v>1920</v>
       </c>
-      <c r="H5" s="31">
+      <c r="H5" s="29">
         <v>2</v>
       </c>
-      <c r="I5" s="8">
+      <c r="I5" s="3">
         <f t="shared" ref="I5:I36" si="0">G5-H5</f>
         <v>1918</v>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="7">
         <f t="shared" ref="J5:J36" si="1">H5/G5</f>
         <v>1.0416666666666667E-3</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="7">
+      <c r="K5" s="43">
+        <f t="shared" ref="K5:K36" si="2">G5*0.0000001+H5*0.008</f>
+        <v>1.6192000000000002E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="6">
         <v>2</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="6">
         <v>64</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="6">
         <v>4</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="6">
         <v>4</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="3">
         <v>1920</v>
       </c>
-      <c r="H6" s="31">
+      <c r="H6" s="29">
         <v>2</v>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="3">
         <f t="shared" si="0"/>
         <v>1918</v>
       </c>
-      <c r="J6" s="9">
+      <c r="J6" s="7">
         <f t="shared" si="1"/>
         <v>1.0416666666666667E-3</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="7">
+      <c r="K6" s="43">
+        <f t="shared" si="2"/>
+        <v>1.6192000000000002E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="6">
         <v>3</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="6">
         <v>64</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="6">
         <v>4</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="6">
         <v>4</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="3">
         <v>1920</v>
       </c>
-      <c r="H7" s="31">
+      <c r="H7" s="29">
         <v>2</v>
       </c>
-      <c r="I7" s="8">
+      <c r="I7" s="3">
         <f t="shared" si="0"/>
         <v>1918</v>
       </c>
-      <c r="J7" s="9">
+      <c r="J7" s="7">
         <f t="shared" si="1"/>
         <v>1.0416666666666667E-3</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="10">
+      <c r="K7" s="43">
+        <f t="shared" si="2"/>
+        <v>1.6192000000000002E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="8">
         <v>4</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="8">
         <v>64</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="8">
         <v>4</v>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="8">
         <v>8</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="9">
         <v>1920</v>
       </c>
-      <c r="H8" s="32">
+      <c r="H8" s="30">
         <v>2</v>
       </c>
-      <c r="I8" s="11">
+      <c r="I8" s="9">
         <f t="shared" si="0"/>
         <v>1918</v>
       </c>
-      <c r="J8" s="12">
+      <c r="J8" s="10">
         <f t="shared" si="1"/>
         <v>1.0416666666666667E-3</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="10">
+      <c r="K8" s="43">
+        <f t="shared" si="2"/>
+        <v>1.6192000000000002E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="8">
         <v>5</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="8">
         <v>64</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="8">
         <v>4</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="8">
         <v>8</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="9">
         <v>1920</v>
       </c>
-      <c r="H9" s="32">
+      <c r="H9" s="30">
         <v>2</v>
       </c>
-      <c r="I9" s="11">
+      <c r="I9" s="9">
         <f t="shared" si="0"/>
         <v>1918</v>
       </c>
-      <c r="J9" s="12">
+      <c r="J9" s="10">
         <f t="shared" si="1"/>
         <v>1.0416666666666667E-3</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="10">
+      <c r="K9" s="43">
+        <f t="shared" si="2"/>
+        <v>1.6192000000000002E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="8">
         <v>6</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="8">
         <v>64</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="8">
         <v>4</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="8">
         <v>8</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="9">
         <v>1920</v>
       </c>
-      <c r="H10" s="32">
+      <c r="H10" s="30">
         <v>2</v>
       </c>
-      <c r="I10" s="11">
+      <c r="I10" s="9">
         <f t="shared" si="0"/>
         <v>1918</v>
       </c>
-      <c r="J10" s="12">
+      <c r="J10" s="10">
         <f t="shared" si="1"/>
         <v>1.0416666666666667E-3</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="7">
+      <c r="K10" s="43">
+        <f t="shared" si="2"/>
+        <v>1.6192000000000002E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="6">
         <v>7</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="6">
         <v>64</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="6">
         <v>4</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="6">
         <v>16</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="3">
         <v>1920</v>
       </c>
-      <c r="H11" s="31">
+      <c r="H11" s="29">
         <v>2</v>
       </c>
-      <c r="I11" s="8">
+      <c r="I11" s="3">
         <f t="shared" si="0"/>
         <v>1918</v>
       </c>
-      <c r="J11" s="9">
+      <c r="J11" s="7">
         <f t="shared" si="1"/>
         <v>1.0416666666666667E-3</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="7">
+      <c r="K11" s="43">
+        <f t="shared" si="2"/>
+        <v>1.6192000000000002E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="6">
         <v>8</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="6">
         <v>64</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="6">
         <v>4</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="6">
         <v>16</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G12" s="3">
         <v>1920</v>
       </c>
-      <c r="H12" s="31">
+      <c r="H12" s="29">
         <v>2</v>
       </c>
-      <c r="I12" s="8">
+      <c r="I12" s="3">
         <f t="shared" si="0"/>
         <v>1918</v>
       </c>
-      <c r="J12" s="9">
+      <c r="J12" s="7">
         <f t="shared" si="1"/>
         <v>1.0416666666666667E-3</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="7">
+      <c r="K12" s="43">
+        <f t="shared" si="2"/>
+        <v>1.6192000000000002E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="6">
         <v>9</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="6">
         <v>64</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="6">
         <v>4</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="6">
         <v>16</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G13" s="3">
         <v>1920</v>
       </c>
-      <c r="H13" s="31">
+      <c r="H13" s="29">
         <v>2</v>
       </c>
-      <c r="I13" s="8">
+      <c r="I13" s="3">
         <f t="shared" si="0"/>
         <v>1918</v>
       </c>
-      <c r="J13" s="9">
+      <c r="J13" s="7">
         <f t="shared" si="1"/>
         <v>1.0416666666666667E-3</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="10">
+      <c r="K13" s="43">
+        <f t="shared" si="2"/>
+        <v>1.6192000000000002E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="8">
         <v>10</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="10">
+      <c r="C14" s="8">
         <v>256</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="8">
         <v>1</v>
       </c>
-      <c r="E14" s="10">
+      <c r="E14" s="8">
         <v>4</v>
       </c>
-      <c r="F14" s="10" t="s">
+      <c r="F14" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="G14" s="11">
+      <c r="G14" s="9">
         <v>1920</v>
       </c>
-      <c r="H14" s="32">
+      <c r="H14" s="30">
         <v>1</v>
       </c>
-      <c r="I14" s="11">
+      <c r="I14" s="9">
         <f t="shared" si="0"/>
         <v>1919</v>
       </c>
-      <c r="J14" s="12">
+      <c r="J14" s="10">
         <f t="shared" si="1"/>
         <v>5.2083333333333333E-4</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="10">
+      <c r="K14" s="43">
+        <f t="shared" si="2"/>
+        <v>8.1919999999999996E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="8">
         <v>11</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="10">
+      <c r="C15" s="8">
         <v>256</v>
       </c>
-      <c r="D15" s="10">
+      <c r="D15" s="8">
         <v>1</v>
       </c>
-      <c r="E15" s="10">
+      <c r="E15" s="8">
         <v>4</v>
       </c>
-      <c r="F15" s="10" t="s">
+      <c r="F15" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="G15" s="11">
+      <c r="G15" s="9">
         <v>1920</v>
       </c>
-      <c r="H15" s="32">
+      <c r="H15" s="30">
         <v>1</v>
       </c>
-      <c r="I15" s="11">
+      <c r="I15" s="9">
         <f t="shared" si="0"/>
         <v>1919</v>
       </c>
-      <c r="J15" s="12">
+      <c r="J15" s="10">
         <f t="shared" si="1"/>
         <v>5.2083333333333333E-4</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="10">
+      <c r="K15" s="43">
+        <f t="shared" si="2"/>
+        <v>8.1919999999999996E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="8">
         <v>12</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="10">
+      <c r="C16" s="8">
         <v>256</v>
       </c>
-      <c r="D16" s="10">
+      <c r="D16" s="8">
         <v>1</v>
       </c>
-      <c r="E16" s="10">
+      <c r="E16" s="8">
         <v>4</v>
       </c>
-      <c r="F16" s="10" t="s">
+      <c r="F16" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G16" s="11">
+      <c r="G16" s="9">
         <v>1920</v>
       </c>
-      <c r="H16" s="32">
+      <c r="H16" s="30">
         <v>1</v>
       </c>
-      <c r="I16" s="11">
+      <c r="I16" s="9">
         <f t="shared" si="0"/>
         <v>1919</v>
       </c>
-      <c r="J16" s="12">
+      <c r="J16" s="10">
         <f t="shared" si="1"/>
         <v>5.2083333333333333E-4</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="7">
+      <c r="K16" s="43">
+        <f t="shared" si="2"/>
+        <v>8.1919999999999996E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="6">
         <v>13</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="6">
         <v>256</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="6">
         <v>1</v>
       </c>
-      <c r="E17" s="7">
+      <c r="E17" s="6">
         <v>8</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F17" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G17" s="8">
+      <c r="G17" s="3">
         <v>1920</v>
       </c>
-      <c r="H17" s="31">
+      <c r="H17" s="29">
         <v>1</v>
       </c>
-      <c r="I17" s="8">
+      <c r="I17" s="3">
         <f t="shared" si="0"/>
         <v>1919</v>
       </c>
-      <c r="J17" s="9">
+      <c r="J17" s="7">
         <f t="shared" si="1"/>
         <v>5.2083333333333333E-4</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="7">
+      <c r="K17" s="43">
+        <f t="shared" si="2"/>
+        <v>8.1919999999999996E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="6">
         <v>14</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="6">
         <v>256</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D18" s="6">
         <v>1</v>
       </c>
-      <c r="E18" s="7">
+      <c r="E18" s="6">
         <v>8</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G18" s="8">
+      <c r="G18" s="3">
         <v>1920</v>
       </c>
-      <c r="H18" s="31">
+      <c r="H18" s="29">
         <v>1</v>
       </c>
-      <c r="I18" s="8">
+      <c r="I18" s="3">
         <f t="shared" si="0"/>
         <v>1919</v>
       </c>
-      <c r="J18" s="9">
+      <c r="J18" s="7">
         <f t="shared" si="1"/>
         <v>5.2083333333333333E-4</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="7">
+      <c r="K18" s="43">
+        <f t="shared" si="2"/>
+        <v>8.1919999999999996E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="6">
         <v>15</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="6">
         <v>256</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="6">
         <v>1</v>
       </c>
-      <c r="E19" s="7">
+      <c r="E19" s="6">
         <v>8</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F19" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G19" s="8">
+      <c r="G19" s="3">
         <v>1920</v>
       </c>
-      <c r="H19" s="31">
+      <c r="H19" s="29">
         <v>1</v>
       </c>
-      <c r="I19" s="8">
+      <c r="I19" s="3">
         <f t="shared" si="0"/>
         <v>1919</v>
       </c>
-      <c r="J19" s="9">
+      <c r="J19" s="7">
         <f t="shared" si="1"/>
         <v>5.2083333333333333E-4</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="10">
+      <c r="K19" s="43">
+        <f t="shared" si="2"/>
+        <v>8.1919999999999996E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="8">
         <v>16</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="10">
+      <c r="C20" s="8">
         <v>256</v>
       </c>
-      <c r="D20" s="10">
+      <c r="D20" s="8">
         <v>1</v>
       </c>
-      <c r="E20" s="10">
+      <c r="E20" s="8">
         <v>16</v>
       </c>
-      <c r="F20" s="10" t="s">
+      <c r="F20" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="G20" s="11">
+      <c r="G20" s="9">
         <v>1920</v>
       </c>
-      <c r="H20" s="32">
+      <c r="H20" s="30">
         <v>1</v>
       </c>
-      <c r="I20" s="11">
+      <c r="I20" s="9">
         <f t="shared" si="0"/>
         <v>1919</v>
       </c>
-      <c r="J20" s="12">
+      <c r="J20" s="10">
         <f t="shared" si="1"/>
         <v>5.2083333333333333E-4</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="10">
+      <c r="K20" s="43">
+        <f t="shared" si="2"/>
+        <v>8.1919999999999996E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="8">
         <v>17</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C21" s="10">
+      <c r="C21" s="8">
         <v>256</v>
       </c>
-      <c r="D21" s="10">
+      <c r="D21" s="8">
         <v>1</v>
       </c>
-      <c r="E21" s="10">
+      <c r="E21" s="8">
         <v>16</v>
       </c>
-      <c r="F21" s="10" t="s">
+      <c r="F21" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="G21" s="11">
+      <c r="G21" s="9">
         <v>1920</v>
       </c>
-      <c r="H21" s="32">
+      <c r="H21" s="30">
         <v>1</v>
       </c>
-      <c r="I21" s="11">
+      <c r="I21" s="9">
         <f t="shared" si="0"/>
         <v>1919</v>
       </c>
-      <c r="J21" s="12">
+      <c r="J21" s="10">
         <f t="shared" si="1"/>
         <v>5.2083333333333333E-4</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="10">
+      <c r="K21" s="43">
+        <f t="shared" si="2"/>
+        <v>8.1919999999999996E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="8">
         <v>18</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C22" s="10">
+      <c r="C22" s="8">
         <v>256</v>
       </c>
-      <c r="D22" s="10">
+      <c r="D22" s="8">
         <v>1</v>
       </c>
-      <c r="E22" s="10">
+      <c r="E22" s="8">
         <v>16</v>
       </c>
-      <c r="F22" s="10" t="s">
+      <c r="F22" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G22" s="11">
+      <c r="G22" s="9">
         <v>1920</v>
       </c>
-      <c r="H22" s="32">
+      <c r="H22" s="30">
         <v>1</v>
       </c>
-      <c r="I22" s="11">
+      <c r="I22" s="9">
         <f t="shared" si="0"/>
         <v>1919</v>
       </c>
-      <c r="J22" s="12">
+      <c r="J22" s="10">
         <f t="shared" si="1"/>
         <v>5.2083333333333333E-4</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="7">
+      <c r="K22" s="43">
+        <f t="shared" si="2"/>
+        <v>8.1919999999999996E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="6">
         <v>19</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="6">
         <v>1024</v>
       </c>
-      <c r="D23" s="7">
+      <c r="D23" s="6">
         <v>1</v>
       </c>
-      <c r="E23" s="7">
+      <c r="E23" s="6">
         <v>4</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="F23" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G23" s="8">
+      <c r="G23" s="3">
         <v>1920</v>
       </c>
-      <c r="H23" s="31">
+      <c r="H23" s="29">
         <v>1</v>
       </c>
-      <c r="I23" s="8">
+      <c r="I23" s="3">
         <f t="shared" si="0"/>
         <v>1919</v>
       </c>
-      <c r="J23" s="9">
+      <c r="J23" s="7">
         <f t="shared" si="1"/>
         <v>5.2083333333333333E-4</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="7">
+      <c r="K23" s="43">
+        <f t="shared" si="2"/>
+        <v>8.1919999999999996E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="6">
         <v>20</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C24" s="6">
         <v>1024</v>
       </c>
-      <c r="D24" s="7">
+      <c r="D24" s="6">
         <v>1</v>
       </c>
-      <c r="E24" s="7">
+      <c r="E24" s="6">
         <v>4</v>
       </c>
-      <c r="F24" s="7" t="s">
+      <c r="F24" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G24" s="8">
+      <c r="G24" s="3">
         <v>1920</v>
       </c>
-      <c r="H24" s="31">
+      <c r="H24" s="29">
         <v>1</v>
       </c>
-      <c r="I24" s="8">
+      <c r="I24" s="3">
         <f t="shared" si="0"/>
         <v>1919</v>
       </c>
-      <c r="J24" s="9">
+      <c r="J24" s="7">
         <f t="shared" si="1"/>
         <v>5.2083333333333333E-4</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="7">
+      <c r="K24" s="43">
+        <f t="shared" si="2"/>
+        <v>8.1919999999999996E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="6">
         <v>21</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C25" s="7">
+      <c r="C25" s="6">
         <v>1024</v>
       </c>
-      <c r="D25" s="7">
+      <c r="D25" s="6">
         <v>1</v>
       </c>
-      <c r="E25" s="7">
+      <c r="E25" s="6">
         <v>4</v>
       </c>
-      <c r="F25" s="7" t="s">
+      <c r="F25" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G25" s="8">
+      <c r="G25" s="3">
         <v>1920</v>
       </c>
-      <c r="H25" s="31">
+      <c r="H25" s="29">
         <v>1</v>
       </c>
-      <c r="I25" s="8">
+      <c r="I25" s="3">
         <f t="shared" si="0"/>
         <v>1919</v>
       </c>
-      <c r="J25" s="9">
+      <c r="J25" s="7">
         <f t="shared" si="1"/>
         <v>5.2083333333333333E-4</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="10">
+      <c r="K25" s="43">
+        <f t="shared" si="2"/>
+        <v>8.1919999999999996E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="8">
         <v>22</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="10">
+      <c r="C26" s="8">
         <v>1024</v>
       </c>
-      <c r="D26" s="10">
+      <c r="D26" s="8">
         <v>1</v>
       </c>
-      <c r="E26" s="10">
+      <c r="E26" s="8">
         <v>8</v>
       </c>
-      <c r="F26" s="10" t="s">
+      <c r="F26" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="G26" s="11">
+      <c r="G26" s="9">
         <v>1920</v>
       </c>
-      <c r="H26" s="32">
+      <c r="H26" s="30">
         <v>1</v>
       </c>
-      <c r="I26" s="11">
+      <c r="I26" s="9">
         <f t="shared" si="0"/>
         <v>1919</v>
       </c>
-      <c r="J26" s="12">
+      <c r="J26" s="10">
         <f t="shared" si="1"/>
         <v>5.2083333333333333E-4</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="10">
+      <c r="K26" s="43">
+        <f t="shared" si="2"/>
+        <v>8.1919999999999996E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="8">
         <v>23</v>
       </c>
-      <c r="B27" s="10" t="s">
+      <c r="B27" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C27" s="10">
+      <c r="C27" s="8">
         <v>1024</v>
       </c>
-      <c r="D27" s="10">
+      <c r="D27" s="8">
         <v>1</v>
       </c>
-      <c r="E27" s="10">
+      <c r="E27" s="8">
         <v>8</v>
       </c>
-      <c r="F27" s="10" t="s">
+      <c r="F27" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="G27" s="11">
+      <c r="G27" s="9">
         <v>1920</v>
       </c>
-      <c r="H27" s="32">
+      <c r="H27" s="30">
         <v>1</v>
       </c>
-      <c r="I27" s="11">
+      <c r="I27" s="9">
         <f t="shared" si="0"/>
         <v>1919</v>
       </c>
-      <c r="J27" s="12">
+      <c r="J27" s="10">
         <f t="shared" si="1"/>
         <v>5.2083333333333333E-4</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="10">
+      <c r="K27" s="43">
+        <f t="shared" si="2"/>
+        <v>8.1919999999999996E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="8">
         <v>24</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B28" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C28" s="10">
+      <c r="C28" s="8">
         <v>1024</v>
       </c>
-      <c r="D28" s="10">
+      <c r="D28" s="8">
         <v>1</v>
       </c>
-      <c r="E28" s="10">
+      <c r="E28" s="8">
         <v>8</v>
       </c>
-      <c r="F28" s="10" t="s">
+      <c r="F28" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G28" s="11">
+      <c r="G28" s="9">
         <v>1920</v>
       </c>
-      <c r="H28" s="32">
+      <c r="H28" s="30">
         <v>1</v>
       </c>
-      <c r="I28" s="11">
+      <c r="I28" s="9">
         <f t="shared" si="0"/>
         <v>1919</v>
       </c>
-      <c r="J28" s="12">
+      <c r="J28" s="10">
         <f t="shared" si="1"/>
         <v>5.2083333333333333E-4</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="7">
+      <c r="K28" s="43">
+        <f t="shared" si="2"/>
+        <v>8.1919999999999996E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="6">
         <v>25</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C29" s="7">
+      <c r="C29" s="6">
         <v>1024</v>
       </c>
-      <c r="D29" s="7">
+      <c r="D29" s="6">
         <v>1</v>
       </c>
-      <c r="E29" s="7">
+      <c r="E29" s="6">
         <v>16</v>
       </c>
-      <c r="F29" s="7" t="s">
+      <c r="F29" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G29" s="8">
+      <c r="G29" s="3">
         <v>1920</v>
       </c>
-      <c r="H29" s="31">
+      <c r="H29" s="29">
         <v>1</v>
       </c>
-      <c r="I29" s="8">
+      <c r="I29" s="3">
         <f t="shared" si="0"/>
         <v>1919</v>
       </c>
-      <c r="J29" s="9">
+      <c r="J29" s="7">
         <f t="shared" si="1"/>
         <v>5.2083333333333333E-4</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="13">
+      <c r="K29" s="43">
+        <f t="shared" si="2"/>
+        <v>8.1919999999999996E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="11">
         <v>26</v>
       </c>
-      <c r="B30" s="13" t="s">
+      <c r="B30" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C30" s="13">
+      <c r="C30" s="11">
         <v>1024</v>
       </c>
-      <c r="D30" s="13">
+      <c r="D30" s="11">
         <v>1</v>
       </c>
-      <c r="E30" s="13">
+      <c r="E30" s="11">
         <v>16</v>
       </c>
-      <c r="F30" s="13" t="s">
+      <c r="F30" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="G30" s="14">
+      <c r="G30" s="12">
         <v>1920</v>
       </c>
-      <c r="H30" s="33">
+      <c r="H30" s="31">
         <v>1</v>
       </c>
-      <c r="I30" s="14">
+      <c r="I30" s="12">
         <f t="shared" si="0"/>
         <v>1919</v>
       </c>
-      <c r="J30" s="15">
+      <c r="J30" s="13">
         <f t="shared" si="1"/>
         <v>5.2083333333333333E-4</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="19">
+      <c r="K30" s="43">
+        <f t="shared" si="2"/>
+        <v>8.1919999999999996E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="17">
         <v>27</v>
       </c>
-      <c r="B31" s="19" t="s">
+      <c r="B31" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="C31" s="19">
+      <c r="C31" s="17">
         <v>1024</v>
       </c>
-      <c r="D31" s="19">
+      <c r="D31" s="17">
         <v>1</v>
       </c>
-      <c r="E31" s="19">
+      <c r="E31" s="17">
         <v>16</v>
       </c>
-      <c r="F31" s="19" t="s">
+      <c r="F31" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="G31" s="20">
+      <c r="G31" s="18">
         <v>1920</v>
       </c>
-      <c r="H31" s="34">
+      <c r="H31" s="32">
         <v>1</v>
       </c>
-      <c r="I31" s="20">
+      <c r="I31" s="18">
         <f t="shared" si="0"/>
         <v>1919</v>
       </c>
-      <c r="J31" s="21">
+      <c r="J31" s="19">
         <f t="shared" si="1"/>
         <v>5.2083333333333333E-4</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="16">
+      <c r="K31" s="43">
+        <f t="shared" si="2"/>
+        <v>8.1919999999999996E-3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="14">
         <v>28</v>
       </c>
-      <c r="B32" s="16" t="s">
+      <c r="B32" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C32" s="16">
+      <c r="C32" s="14">
         <v>64</v>
       </c>
-      <c r="D32" s="16">
+      <c r="D32" s="14">
         <v>7</v>
       </c>
-      <c r="E32" s="16">
+      <c r="E32" s="14">
         <v>4</v>
       </c>
-      <c r="F32" s="16" t="s">
+      <c r="F32" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="G32" s="17">
+      <c r="G32" s="15">
         <v>7680</v>
       </c>
-      <c r="H32" s="35">
+      <c r="H32" s="33">
         <v>425</v>
       </c>
-      <c r="I32" s="17">
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
         <v>7255</v>
       </c>
-      <c r="J32" s="18">
+      <c r="J32" s="16">
         <f t="shared" si="1"/>
         <v>5.5338541666666664E-2</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="10">
+      <c r="K32" s="43">
+        <f t="shared" si="2"/>
+        <v>3.4007679999999998</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="8">
         <v>29</v>
       </c>
-      <c r="B33" s="10" t="s">
+      <c r="B33" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C33" s="10">
+      <c r="C33" s="8">
         <v>64</v>
       </c>
-      <c r="D33" s="10">
+      <c r="D33" s="8">
         <v>7</v>
       </c>
-      <c r="E33" s="10">
+      <c r="E33" s="8">
         <v>4</v>
       </c>
-      <c r="F33" s="10" t="s">
+      <c r="F33" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="G33" s="11">
+      <c r="G33" s="9">
         <v>7680</v>
       </c>
-      <c r="H33" s="32">
+      <c r="H33" s="30">
         <v>341</v>
       </c>
-      <c r="I33" s="11">
+      <c r="I33" s="9">
         <f t="shared" si="0"/>
         <v>7339</v>
       </c>
-      <c r="J33" s="12">
+      <c r="J33" s="10">
         <f t="shared" si="1"/>
         <v>4.4401041666666669E-2</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="10">
+      <c r="K33" s="43">
+        <f t="shared" si="2"/>
+        <v>2.7287680000000001</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="8">
         <v>30</v>
       </c>
-      <c r="B34" s="10" t="s">
+      <c r="B34" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C34" s="10">
+      <c r="C34" s="8">
         <v>64</v>
       </c>
-      <c r="D34" s="10">
+      <c r="D34" s="8">
         <v>7</v>
       </c>
-      <c r="E34" s="10">
+      <c r="E34" s="8">
         <v>4</v>
       </c>
-      <c r="F34" s="10" t="s">
+      <c r="F34" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G34" s="11">
+      <c r="G34" s="9">
         <v>7680</v>
       </c>
-      <c r="H34" s="32">
+      <c r="H34" s="30">
         <v>341</v>
       </c>
-      <c r="I34" s="11">
+      <c r="I34" s="9">
         <f t="shared" si="0"/>
         <v>7339</v>
       </c>
-      <c r="J34" s="12">
+      <c r="J34" s="10">
         <f t="shared" si="1"/>
         <v>4.4401041666666669E-2</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="7">
+      <c r="K34" s="43">
+        <f t="shared" si="2"/>
+        <v>2.7287680000000001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="6">
         <v>31</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="B35" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C35" s="7">
+      <c r="C35" s="6">
         <v>64</v>
       </c>
-      <c r="D35" s="7">
+      <c r="D35" s="6">
         <v>7</v>
       </c>
-      <c r="E35" s="7">
+      <c r="E35" s="6">
         <v>8</v>
       </c>
-      <c r="F35" s="7" t="s">
+      <c r="F35" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G35" s="8">
+      <c r="G35" s="3">
         <v>7680</v>
       </c>
-      <c r="H35" s="31">
+      <c r="H35" s="29">
         <v>5</v>
       </c>
-      <c r="I35" s="8">
+      <c r="I35" s="3">
         <f t="shared" si="0"/>
         <v>7675</v>
       </c>
-      <c r="J35" s="9">
+      <c r="J35" s="7">
         <f t="shared" si="1"/>
         <v>6.5104166666666663E-4</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="7">
+      <c r="K35" s="43">
+        <f t="shared" si="2"/>
+        <v>4.0767999999999999E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="6">
         <v>32</v>
       </c>
-      <c r="B36" s="7" t="s">
+      <c r="B36" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C36" s="7">
+      <c r="C36" s="6">
         <v>64</v>
       </c>
-      <c r="D36" s="7">
+      <c r="D36" s="6">
         <v>7</v>
       </c>
-      <c r="E36" s="7">
+      <c r="E36" s="6">
         <v>8</v>
       </c>
-      <c r="F36" s="7" t="s">
+      <c r="F36" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G36" s="8">
+      <c r="G36" s="3">
         <v>7680</v>
       </c>
-      <c r="H36" s="31">
+      <c r="H36" s="29">
         <v>5</v>
       </c>
-      <c r="I36" s="8">
+      <c r="I36" s="3">
         <f t="shared" si="0"/>
         <v>7675</v>
       </c>
-      <c r="J36" s="9">
+      <c r="J36" s="7">
         <f t="shared" si="1"/>
         <v>6.5104166666666663E-4</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="7">
+      <c r="K36" s="43">
+        <f t="shared" si="2"/>
+        <v>4.0767999999999999E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="6">
         <v>33</v>
       </c>
-      <c r="B37" s="7" t="s">
+      <c r="B37" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C37" s="7">
+      <c r="C37" s="6">
         <v>64</v>
       </c>
-      <c r="D37" s="7">
+      <c r="D37" s="6">
         <v>7</v>
       </c>
-      <c r="E37" s="7">
+      <c r="E37" s="6">
         <v>8</v>
       </c>
-      <c r="F37" s="7" t="s">
+      <c r="F37" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G37" s="8">
+      <c r="G37" s="3">
         <v>7680</v>
       </c>
-      <c r="H37" s="31">
+      <c r="H37" s="29">
         <v>5</v>
       </c>
-      <c r="I37" s="8">
-        <f t="shared" ref="I37:I68" si="2">G37-H37</f>
+      <c r="I37" s="3">
+        <f t="shared" ref="I37:I68" si="3">G37-H37</f>
         <v>7675</v>
       </c>
-      <c r="J37" s="9">
-        <f t="shared" ref="J37:J68" si="3">H37/G37</f>
+      <c r="J37" s="7">
+        <f t="shared" ref="J37:J68" si="4">H37/G37</f>
         <v>6.5104166666666663E-4</v>
       </c>
-    </row>
-    <row r="38" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="10">
+      <c r="K37" s="43">
+        <f t="shared" ref="K37:K68" si="5">G37*0.0000001+H37*0.008</f>
+        <v>4.0767999999999999E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="8">
         <v>34</v>
       </c>
-      <c r="B38" s="10" t="s">
+      <c r="B38" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C38" s="10">
+      <c r="C38" s="8">
         <v>64</v>
       </c>
-      <c r="D38" s="10">
+      <c r="D38" s="8">
         <v>7</v>
       </c>
-      <c r="E38" s="10">
+      <c r="E38" s="8">
         <v>16</v>
       </c>
-      <c r="F38" s="10" t="s">
+      <c r="F38" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="G38" s="11">
+      <c r="G38" s="9">
         <v>7680</v>
       </c>
-      <c r="H38" s="32">
+      <c r="H38" s="30">
         <v>5</v>
       </c>
-      <c r="I38" s="11">
-        <f t="shared" si="2"/>
+      <c r="I38" s="9">
+        <f t="shared" si="3"/>
         <v>7675</v>
       </c>
-      <c r="J38" s="12">
+      <c r="J38" s="10">
+        <f t="shared" si="4"/>
+        <v>6.5104166666666663E-4</v>
+      </c>
+      <c r="K38" s="43">
+        <f t="shared" si="5"/>
+        <v>4.0767999999999999E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="8">
+        <v>35</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" s="8">
+        <v>64</v>
+      </c>
+      <c r="D39" s="8">
+        <v>7</v>
+      </c>
+      <c r="E39" s="8">
+        <v>16</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G39" s="9">
+        <v>7680</v>
+      </c>
+      <c r="H39" s="30">
+        <v>5</v>
+      </c>
+      <c r="I39" s="9">
         <f t="shared" si="3"/>
+        <v>7675</v>
+      </c>
+      <c r="J39" s="10">
+        <f t="shared" si="4"/>
         <v>6.5104166666666663E-4</v>
       </c>
-    </row>
-    <row r="39" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="10">
-        <v>35</v>
-      </c>
-      <c r="B39" s="10" t="s">
+      <c r="K39" s="43">
+        <f t="shared" si="5"/>
+        <v>4.0767999999999999E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="8">
+        <v>36</v>
+      </c>
+      <c r="B40" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C39" s="10">
+      <c r="C40" s="8">
         <v>64</v>
       </c>
-      <c r="D39" s="10">
+      <c r="D40" s="8">
         <v>7</v>
       </c>
-      <c r="E39" s="10">
+      <c r="E40" s="8">
         <v>16</v>
       </c>
-      <c r="F39" s="10" t="s">
+      <c r="F40" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G40" s="9">
+        <v>7680</v>
+      </c>
+      <c r="H40" s="30">
+        <v>5</v>
+      </c>
+      <c r="I40" s="9">
+        <f t="shared" si="3"/>
+        <v>7675</v>
+      </c>
+      <c r="J40" s="10">
+        <f t="shared" si="4"/>
+        <v>6.5104166666666663E-4</v>
+      </c>
+      <c r="K40" s="43">
+        <f t="shared" si="5"/>
+        <v>4.0767999999999999E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="6">
+        <v>37</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" s="6">
+        <v>256</v>
+      </c>
+      <c r="D41" s="6">
+        <v>2</v>
+      </c>
+      <c r="E41" s="6">
+        <v>4</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G41" s="3">
+        <v>7680</v>
+      </c>
+      <c r="H41" s="29">
+        <v>2</v>
+      </c>
+      <c r="I41" s="3">
+        <f t="shared" si="3"/>
+        <v>7678</v>
+      </c>
+      <c r="J41" s="7">
+        <f t="shared" si="4"/>
+        <v>2.6041666666666666E-4</v>
+      </c>
+      <c r="K41" s="43">
+        <f t="shared" si="5"/>
+        <v>1.6768000000000002E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="6">
+        <v>38</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" s="6">
+        <v>256</v>
+      </c>
+      <c r="D42" s="6">
+        <v>2</v>
+      </c>
+      <c r="E42" s="6">
+        <v>4</v>
+      </c>
+      <c r="F42" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G39" s="11">
+      <c r="G42" s="3">
         <v>7680</v>
       </c>
-      <c r="H39" s="32">
-        <v>5</v>
-      </c>
-      <c r="I39" s="11">
-        <f t="shared" si="2"/>
-        <v>7675</v>
-      </c>
-      <c r="J39" s="12">
+      <c r="H42" s="29">
+        <v>2</v>
+      </c>
+      <c r="I42" s="3">
         <f t="shared" si="3"/>
-        <v>6.5104166666666663E-4</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="10">
-        <v>36</v>
-      </c>
-      <c r="B40" s="10" t="s">
+        <v>7678</v>
+      </c>
+      <c r="J42" s="7">
+        <f t="shared" si="4"/>
+        <v>2.6041666666666666E-4</v>
+      </c>
+      <c r="K42" s="43">
+        <f t="shared" si="5"/>
+        <v>1.6768000000000002E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="6">
+        <v>39</v>
+      </c>
+      <c r="B43" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C40" s="10">
+      <c r="C43" s="6">
+        <v>256</v>
+      </c>
+      <c r="D43" s="6">
+        <v>2</v>
+      </c>
+      <c r="E43" s="6">
+        <v>4</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G43" s="3">
+        <v>7680</v>
+      </c>
+      <c r="H43" s="29">
+        <v>2</v>
+      </c>
+      <c r="I43" s="3">
+        <f t="shared" si="3"/>
+        <v>7678</v>
+      </c>
+      <c r="J43" s="7">
+        <f t="shared" si="4"/>
+        <v>2.6041666666666666E-4</v>
+      </c>
+      <c r="K43" s="43">
+        <f t="shared" si="5"/>
+        <v>1.6768000000000002E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="8">
+        <v>40</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" s="8">
+        <v>256</v>
+      </c>
+      <c r="D44" s="8">
+        <v>2</v>
+      </c>
+      <c r="E44" s="8">
+        <v>8</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G44" s="9">
+        <v>7680</v>
+      </c>
+      <c r="H44" s="30">
+        <v>2</v>
+      </c>
+      <c r="I44" s="9">
+        <f t="shared" si="3"/>
+        <v>7678</v>
+      </c>
+      <c r="J44" s="10">
+        <f t="shared" si="4"/>
+        <v>2.6041666666666666E-4</v>
+      </c>
+      <c r="K44" s="43">
+        <f t="shared" si="5"/>
+        <v>1.6768000000000002E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="8">
+        <v>41</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" s="8">
+        <v>256</v>
+      </c>
+      <c r="D45" s="8">
+        <v>2</v>
+      </c>
+      <c r="E45" s="8">
+        <v>8</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G45" s="9">
+        <v>7680</v>
+      </c>
+      <c r="H45" s="30">
+        <v>2</v>
+      </c>
+      <c r="I45" s="9">
+        <f t="shared" si="3"/>
+        <v>7678</v>
+      </c>
+      <c r="J45" s="10">
+        <f t="shared" si="4"/>
+        <v>2.6041666666666666E-4</v>
+      </c>
+      <c r="K45" s="43">
+        <f t="shared" si="5"/>
+        <v>1.6768000000000002E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="8">
+        <v>42</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" s="8">
+        <v>256</v>
+      </c>
+      <c r="D46" s="8">
+        <v>2</v>
+      </c>
+      <c r="E46" s="8">
+        <v>8</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G46" s="9">
+        <v>7680</v>
+      </c>
+      <c r="H46" s="30">
+        <v>2</v>
+      </c>
+      <c r="I46" s="9">
+        <f t="shared" si="3"/>
+        <v>7678</v>
+      </c>
+      <c r="J46" s="10">
+        <f t="shared" si="4"/>
+        <v>2.6041666666666666E-4</v>
+      </c>
+      <c r="K46" s="43">
+        <f t="shared" si="5"/>
+        <v>1.6768000000000002E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="6">
+        <v>43</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" s="6">
+        <v>256</v>
+      </c>
+      <c r="D47" s="6">
+        <v>2</v>
+      </c>
+      <c r="E47" s="6">
+        <v>16</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G47" s="3">
+        <v>7680</v>
+      </c>
+      <c r="H47" s="29">
+        <v>2</v>
+      </c>
+      <c r="I47" s="3">
+        <f t="shared" si="3"/>
+        <v>7678</v>
+      </c>
+      <c r="J47" s="7">
+        <f t="shared" si="4"/>
+        <v>2.6041666666666666E-4</v>
+      </c>
+      <c r="K47" s="43">
+        <f t="shared" si="5"/>
+        <v>1.6768000000000002E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="6">
+        <v>44</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" s="6">
+        <v>256</v>
+      </c>
+      <c r="D48" s="6">
+        <v>2</v>
+      </c>
+      <c r="E48" s="6">
+        <v>16</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G48" s="3">
+        <v>7680</v>
+      </c>
+      <c r="H48" s="29">
+        <v>2</v>
+      </c>
+      <c r="I48" s="3">
+        <f t="shared" si="3"/>
+        <v>7678</v>
+      </c>
+      <c r="J48" s="7">
+        <f t="shared" si="4"/>
+        <v>2.6041666666666666E-4</v>
+      </c>
+      <c r="K48" s="43">
+        <f t="shared" si="5"/>
+        <v>1.6768000000000002E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="6">
+        <v>45</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" s="6">
+        <v>256</v>
+      </c>
+      <c r="D49" s="6">
+        <v>2</v>
+      </c>
+      <c r="E49" s="6">
+        <v>16</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G49" s="3">
+        <v>7680</v>
+      </c>
+      <c r="H49" s="29">
+        <v>2</v>
+      </c>
+      <c r="I49" s="3">
+        <f t="shared" si="3"/>
+        <v>7678</v>
+      </c>
+      <c r="J49" s="7">
+        <f t="shared" si="4"/>
+        <v>2.6041666666666666E-4</v>
+      </c>
+      <c r="K49" s="43">
+        <f t="shared" si="5"/>
+        <v>1.6768000000000002E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="8">
+        <v>46</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" s="8">
+        <v>1024</v>
+      </c>
+      <c r="D50" s="8">
+        <v>1</v>
+      </c>
+      <c r="E50" s="8">
+        <v>4</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G50" s="9">
+        <v>7680</v>
+      </c>
+      <c r="H50" s="30">
+        <v>1</v>
+      </c>
+      <c r="I50" s="9">
+        <f t="shared" si="3"/>
+        <v>7679</v>
+      </c>
+      <c r="J50" s="10">
+        <f t="shared" si="4"/>
+        <v>1.3020833333333333E-4</v>
+      </c>
+      <c r="K50" s="43">
+        <f t="shared" si="5"/>
+        <v>8.7679999999999998E-3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="8">
+        <v>47</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" s="8">
+        <v>1024</v>
+      </c>
+      <c r="D51" s="8">
+        <v>1</v>
+      </c>
+      <c r="E51" s="8">
+        <v>4</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G51" s="9">
+        <v>7680</v>
+      </c>
+      <c r="H51" s="30">
+        <v>1</v>
+      </c>
+      <c r="I51" s="9">
+        <f t="shared" si="3"/>
+        <v>7679</v>
+      </c>
+      <c r="J51" s="10">
+        <f t="shared" si="4"/>
+        <v>1.3020833333333333E-4</v>
+      </c>
+      <c r="K51" s="43">
+        <f t="shared" si="5"/>
+        <v>8.7679999999999998E-3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="8">
+        <v>48</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52" s="8">
+        <v>1024</v>
+      </c>
+      <c r="D52" s="8">
+        <v>1</v>
+      </c>
+      <c r="E52" s="8">
+        <v>4</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G52" s="9">
+        <v>7680</v>
+      </c>
+      <c r="H52" s="30">
+        <v>1</v>
+      </c>
+      <c r="I52" s="9">
+        <f t="shared" si="3"/>
+        <v>7679</v>
+      </c>
+      <c r="J52" s="10">
+        <f t="shared" si="4"/>
+        <v>1.3020833333333333E-4</v>
+      </c>
+      <c r="K52" s="43">
+        <f t="shared" si="5"/>
+        <v>8.7679999999999998E-3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="6">
+        <v>49</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C53" s="6">
+        <v>1024</v>
+      </c>
+      <c r="D53" s="6">
+        <v>1</v>
+      </c>
+      <c r="E53" s="6">
+        <v>8</v>
+      </c>
+      <c r="F53" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G53" s="3">
+        <v>7680</v>
+      </c>
+      <c r="H53" s="29">
+        <v>1</v>
+      </c>
+      <c r="I53" s="3">
+        <f t="shared" si="3"/>
+        <v>7679</v>
+      </c>
+      <c r="J53" s="7">
+        <f t="shared" si="4"/>
+        <v>1.3020833333333333E-4</v>
+      </c>
+      <c r="K53" s="43">
+        <f t="shared" si="5"/>
+        <v>8.7679999999999998E-3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="6">
+        <v>50</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" s="6">
+        <v>1024</v>
+      </c>
+      <c r="D54" s="6">
+        <v>1</v>
+      </c>
+      <c r="E54" s="6">
+        <v>8</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G54" s="3">
+        <v>7680</v>
+      </c>
+      <c r="H54" s="29">
+        <v>1</v>
+      </c>
+      <c r="I54" s="3">
+        <f t="shared" si="3"/>
+        <v>7679</v>
+      </c>
+      <c r="J54" s="7">
+        <f t="shared" si="4"/>
+        <v>1.3020833333333333E-4</v>
+      </c>
+      <c r="K54" s="43">
+        <f t="shared" si="5"/>
+        <v>8.7679999999999998E-3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="6">
+        <v>51</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" s="6">
+        <v>1024</v>
+      </c>
+      <c r="D55" s="6">
+        <v>1</v>
+      </c>
+      <c r="E55" s="6">
+        <v>8</v>
+      </c>
+      <c r="F55" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G55" s="3">
+        <v>7680</v>
+      </c>
+      <c r="H55" s="29">
+        <v>1</v>
+      </c>
+      <c r="I55" s="3">
+        <f t="shared" si="3"/>
+        <v>7679</v>
+      </c>
+      <c r="J55" s="7">
+        <f t="shared" si="4"/>
+        <v>1.3020833333333333E-4</v>
+      </c>
+      <c r="K55" s="43">
+        <f t="shared" si="5"/>
+        <v>8.7679999999999998E-3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="8">
+        <v>52</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" s="8">
+        <v>1024</v>
+      </c>
+      <c r="D56" s="8">
+        <v>1</v>
+      </c>
+      <c r="E56" s="8">
+        <v>16</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G56" s="9">
+        <v>7680</v>
+      </c>
+      <c r="H56" s="30">
+        <v>1</v>
+      </c>
+      <c r="I56" s="9">
+        <f t="shared" si="3"/>
+        <v>7679</v>
+      </c>
+      <c r="J56" s="10">
+        <f t="shared" si="4"/>
+        <v>1.3020833333333333E-4</v>
+      </c>
+      <c r="K56" s="43">
+        <f t="shared" si="5"/>
+        <v>8.7679999999999998E-3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="20">
+        <v>53</v>
+      </c>
+      <c r="B57" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" s="20">
+        <v>1024</v>
+      </c>
+      <c r="D57" s="20">
+        <v>1</v>
+      </c>
+      <c r="E57" s="20">
+        <v>16</v>
+      </c>
+      <c r="F57" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="G57" s="21">
+        <v>7680</v>
+      </c>
+      <c r="H57" s="34">
+        <v>1</v>
+      </c>
+      <c r="I57" s="21">
+        <f t="shared" si="3"/>
+        <v>7679</v>
+      </c>
+      <c r="J57" s="22">
+        <f t="shared" si="4"/>
+        <v>1.3020833333333333E-4</v>
+      </c>
+      <c r="K57" s="43">
+        <f t="shared" si="5"/>
+        <v>8.7679999999999998E-3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="26">
+        <v>54</v>
+      </c>
+      <c r="B58" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C58" s="26">
+        <v>1024</v>
+      </c>
+      <c r="D58" s="26">
+        <v>1</v>
+      </c>
+      <c r="E58" s="26">
+        <v>16</v>
+      </c>
+      <c r="F58" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="G58" s="27">
+        <v>7680</v>
+      </c>
+      <c r="H58" s="35">
+        <v>1</v>
+      </c>
+      <c r="I58" s="27">
+        <f t="shared" si="3"/>
+        <v>7679</v>
+      </c>
+      <c r="J58" s="28">
+        <f t="shared" si="4"/>
+        <v>1.3020833333333333E-4</v>
+      </c>
+      <c r="K58" s="43">
+        <f t="shared" si="5"/>
+        <v>8.7679999999999998E-3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="23">
+        <v>55</v>
+      </c>
+      <c r="B59" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C59" s="23">
         <v>64</v>
       </c>
-      <c r="D40" s="10">
-        <v>7</v>
-      </c>
-      <c r="E40" s="10">
+      <c r="D59" s="23">
+        <v>259</v>
+      </c>
+      <c r="E59" s="23">
+        <v>4</v>
+      </c>
+      <c r="F59" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="G59" s="24">
+        <v>491520</v>
+      </c>
+      <c r="H59" s="36">
+        <v>104320</v>
+      </c>
+      <c r="I59" s="24">
+        <f t="shared" si="3"/>
+        <v>387200</v>
+      </c>
+      <c r="J59" s="25">
+        <f t="shared" si="4"/>
+        <v>0.21223958333333334</v>
+      </c>
+      <c r="K59" s="43">
+        <f t="shared" si="5"/>
+        <v>834.60915200000011</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="6">
+        <v>56</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C60" s="6">
+        <v>64</v>
+      </c>
+      <c r="D60" s="6">
+        <v>259</v>
+      </c>
+      <c r="E60" s="6">
+        <v>4</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G60" s="3">
+        <v>491520</v>
+      </c>
+      <c r="H60" s="29">
+        <v>85760</v>
+      </c>
+      <c r="I60" s="3">
+        <f t="shared" si="3"/>
+        <v>405760</v>
+      </c>
+      <c r="J60" s="7">
+        <f t="shared" si="4"/>
+        <v>0.17447916666666666</v>
+      </c>
+      <c r="K60" s="43">
+        <f t="shared" si="5"/>
+        <v>686.12915200000009</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="6">
+        <v>57</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C61" s="6">
+        <v>64</v>
+      </c>
+      <c r="D61" s="6">
+        <v>259</v>
+      </c>
+      <c r="E61" s="6">
+        <v>4</v>
+      </c>
+      <c r="F61" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G61" s="3">
+        <v>491520</v>
+      </c>
+      <c r="H61" s="29">
+        <v>85760</v>
+      </c>
+      <c r="I61" s="3">
+        <f t="shared" si="3"/>
+        <v>405760</v>
+      </c>
+      <c r="J61" s="7">
+        <f t="shared" si="4"/>
+        <v>0.17447916666666666</v>
+      </c>
+      <c r="K61" s="43">
+        <f t="shared" si="5"/>
+        <v>686.12915200000009</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="8">
+        <v>58</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C62" s="8">
+        <v>64</v>
+      </c>
+      <c r="D62" s="8">
+        <v>259</v>
+      </c>
+      <c r="E62" s="8">
+        <v>8</v>
+      </c>
+      <c r="F62" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G62" s="9">
+        <v>491520</v>
+      </c>
+      <c r="H62" s="30">
+        <v>93760</v>
+      </c>
+      <c r="I62" s="9">
+        <f t="shared" si="3"/>
+        <v>397760</v>
+      </c>
+      <c r="J62" s="10">
+        <f t="shared" si="4"/>
+        <v>0.19075520833333334</v>
+      </c>
+      <c r="K62" s="43">
+        <f t="shared" si="5"/>
+        <v>750.12915200000009</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="8">
+        <v>59</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C63" s="8">
+        <v>64</v>
+      </c>
+      <c r="D63" s="8">
+        <v>259</v>
+      </c>
+      <c r="E63" s="8">
+        <v>8</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G63" s="9">
+        <v>491520</v>
+      </c>
+      <c r="H63" s="30">
+        <v>84481</v>
+      </c>
+      <c r="I63" s="9">
+        <f t="shared" si="3"/>
+        <v>407039</v>
+      </c>
+      <c r="J63" s="10">
+        <f t="shared" si="4"/>
+        <v>0.17187703450520833</v>
+      </c>
+      <c r="K63" s="43">
+        <f t="shared" si="5"/>
+        <v>675.89715200000012</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="8">
+        <v>60</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C64" s="8">
+        <v>64</v>
+      </c>
+      <c r="D64" s="8">
+        <v>259</v>
+      </c>
+      <c r="E64" s="8">
+        <v>8</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G64" s="9">
+        <v>491520</v>
+      </c>
+      <c r="H64" s="30">
+        <v>84481</v>
+      </c>
+      <c r="I64" s="9">
+        <f t="shared" si="3"/>
+        <v>407039</v>
+      </c>
+      <c r="J64" s="10">
+        <f t="shared" si="4"/>
+        <v>0.17187703450520833</v>
+      </c>
+      <c r="K64" s="43">
+        <f t="shared" si="5"/>
+        <v>675.89715200000012</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="6">
+        <v>61</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C65" s="6">
+        <v>64</v>
+      </c>
+      <c r="D65" s="6">
+        <v>259</v>
+      </c>
+      <c r="E65" s="6">
         <v>16</v>
       </c>
-      <c r="F40" s="10" t="s">
+      <c r="F65" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G65" s="3">
+        <v>491520</v>
+      </c>
+      <c r="H65" s="29">
+        <v>88480</v>
+      </c>
+      <c r="I65" s="3">
+        <f t="shared" si="3"/>
+        <v>403040</v>
+      </c>
+      <c r="J65" s="7">
+        <f t="shared" si="4"/>
+        <v>0.18001302083333334</v>
+      </c>
+      <c r="K65" s="43">
+        <f t="shared" si="5"/>
+        <v>707.88915200000008</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="6">
+        <v>62</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C66" s="6">
+        <v>64</v>
+      </c>
+      <c r="D66" s="6">
+        <v>259</v>
+      </c>
+      <c r="E66" s="6">
+        <v>16</v>
+      </c>
+      <c r="F66" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G66" s="3">
+        <v>491520</v>
+      </c>
+      <c r="H66" s="29">
+        <v>84481</v>
+      </c>
+      <c r="I66" s="3">
+        <f t="shared" si="3"/>
+        <v>407039</v>
+      </c>
+      <c r="J66" s="7">
+        <f t="shared" si="4"/>
+        <v>0.17187703450520833</v>
+      </c>
+      <c r="K66" s="43">
+        <f t="shared" si="5"/>
+        <v>675.89715200000012</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="6">
+        <v>63</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C67" s="6">
+        <v>64</v>
+      </c>
+      <c r="D67" s="6">
+        <v>259</v>
+      </c>
+      <c r="E67" s="6">
+        <v>16</v>
+      </c>
+      <c r="F67" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G40" s="11">
-        <v>7680</v>
-      </c>
-      <c r="H40" s="32">
-        <v>5</v>
-      </c>
-      <c r="I40" s="11">
-        <f t="shared" si="2"/>
-        <v>7675</v>
-      </c>
-      <c r="J40" s="12">
+      <c r="G67" s="3">
+        <v>491520</v>
+      </c>
+      <c r="H67" s="29">
+        <v>84481</v>
+      </c>
+      <c r="I67" s="3">
         <f t="shared" si="3"/>
-        <v>6.5104166666666663E-4</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="7">
-        <v>37</v>
-      </c>
-      <c r="B41" s="7" t="s">
+        <v>407039</v>
+      </c>
+      <c r="J67" s="7">
+        <f t="shared" si="4"/>
+        <v>0.17187703450520833</v>
+      </c>
+      <c r="K67" s="43">
+        <f t="shared" si="5"/>
+        <v>675.89715200000012</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="8">
+        <v>64</v>
+      </c>
+      <c r="B68" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C68" s="8">
+        <v>256</v>
+      </c>
+      <c r="D68" s="8">
+        <v>65</v>
+      </c>
+      <c r="E68" s="8">
+        <v>4</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G68" s="9">
+        <v>491520</v>
+      </c>
+      <c r="H68" s="30">
+        <v>51600</v>
+      </c>
+      <c r="I68" s="9">
+        <f t="shared" si="3"/>
+        <v>439920</v>
+      </c>
+      <c r="J68" s="10">
+        <f t="shared" si="4"/>
+        <v>0.10498046875</v>
+      </c>
+      <c r="K68" s="43">
+        <f t="shared" si="5"/>
+        <v>412.849152</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="8">
+        <v>65</v>
+      </c>
+      <c r="B69" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C69" s="8">
+        <v>256</v>
+      </c>
+      <c r="D69" s="8">
+        <v>65</v>
+      </c>
+      <c r="E69" s="8">
+        <v>4</v>
+      </c>
+      <c r="F69" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G69" s="9">
+        <v>491520</v>
+      </c>
+      <c r="H69" s="30">
+        <v>41281</v>
+      </c>
+      <c r="I69" s="9">
+        <f t="shared" ref="I69:I85" si="6">G69-H69</f>
+        <v>450239</v>
+      </c>
+      <c r="J69" s="10">
+        <f t="shared" ref="J69:J85" si="7">H69/G69</f>
+        <v>8.3986409505208331E-2</v>
+      </c>
+      <c r="K69" s="43">
+        <f t="shared" ref="K69:K85" si="8">G69*0.0000001+H69*0.008</f>
+        <v>330.29715199999998</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="8">
+        <v>66</v>
+      </c>
+      <c r="B70" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C70" s="8">
+        <v>256</v>
+      </c>
+      <c r="D70" s="8">
+        <v>65</v>
+      </c>
+      <c r="E70" s="8">
+        <v>4</v>
+      </c>
+      <c r="F70" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G70" s="9">
+        <v>491520</v>
+      </c>
+      <c r="H70" s="30">
+        <v>41281</v>
+      </c>
+      <c r="I70" s="9">
+        <f t="shared" si="6"/>
+        <v>450239</v>
+      </c>
+      <c r="J70" s="10">
+        <f t="shared" si="7"/>
+        <v>8.3986409505208331E-2</v>
+      </c>
+      <c r="K70" s="43">
+        <f t="shared" si="8"/>
+        <v>330.29715199999998</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="6">
+        <v>67</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C71" s="6">
+        <v>256</v>
+      </c>
+      <c r="D71" s="6">
+        <v>65</v>
+      </c>
+      <c r="E71" s="6">
+        <v>8</v>
+      </c>
+      <c r="F71" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G71" s="3">
+        <v>491520</v>
+      </c>
+      <c r="H71" s="29">
+        <v>46440</v>
+      </c>
+      <c r="I71" s="3">
+        <f t="shared" si="6"/>
+        <v>445080</v>
+      </c>
+      <c r="J71" s="7">
+        <f t="shared" si="7"/>
+        <v>9.4482421875E-2</v>
+      </c>
+      <c r="K71" s="43">
+        <f t="shared" si="8"/>
+        <v>371.56915199999997</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="6">
+        <v>68</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C72" s="6">
+        <v>256</v>
+      </c>
+      <c r="D72" s="6">
+        <v>65</v>
+      </c>
+      <c r="E72" s="6">
+        <v>8</v>
+      </c>
+      <c r="F72" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G72" s="3">
+        <v>491520</v>
+      </c>
+      <c r="H72" s="29">
+        <v>41281</v>
+      </c>
+      <c r="I72" s="3">
+        <f t="shared" si="6"/>
+        <v>450239</v>
+      </c>
+      <c r="J72" s="7">
+        <f t="shared" si="7"/>
+        <v>8.3986409505208331E-2</v>
+      </c>
+      <c r="K72" s="43">
+        <f t="shared" si="8"/>
+        <v>330.29715199999998</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="6">
+        <v>69</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C73" s="6">
+        <v>256</v>
+      </c>
+      <c r="D73" s="6">
+        <v>65</v>
+      </c>
+      <c r="E73" s="6">
+        <v>8</v>
+      </c>
+      <c r="F73" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G73" s="3">
+        <v>491520</v>
+      </c>
+      <c r="H73" s="29">
+        <v>41281</v>
+      </c>
+      <c r="I73" s="3">
+        <f t="shared" si="6"/>
+        <v>450239</v>
+      </c>
+      <c r="J73" s="7">
+        <f t="shared" si="7"/>
+        <v>8.3986409505208331E-2</v>
+      </c>
+      <c r="K73" s="43">
+        <f t="shared" si="8"/>
+        <v>330.29715199999998</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="8">
+        <v>70</v>
+      </c>
+      <c r="B74" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C74" s="8">
+        <v>256</v>
+      </c>
+      <c r="D74" s="8">
+        <v>65</v>
+      </c>
+      <c r="E74" s="8">
         <v>16</v>
       </c>
-      <c r="C41" s="7">
+      <c r="F74" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G74" s="9">
+        <v>491520</v>
+      </c>
+      <c r="H74" s="30">
+        <v>43860</v>
+      </c>
+      <c r="I74" s="9">
+        <f t="shared" si="6"/>
+        <v>447660</v>
+      </c>
+      <c r="J74" s="10">
+        <f t="shared" si="7"/>
+        <v>8.92333984375E-2</v>
+      </c>
+      <c r="K74" s="43">
+        <f t="shared" si="8"/>
+        <v>350.92915199999999</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="8">
+        <v>71</v>
+      </c>
+      <c r="B75" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C75" s="8">
         <v>256</v>
       </c>
-      <c r="D41" s="7">
-        <v>2</v>
-      </c>
-      <c r="E41" s="7">
+      <c r="D75" s="8">
+        <v>65</v>
+      </c>
+      <c r="E75" s="8">
+        <v>16</v>
+      </c>
+      <c r="F75" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G75" s="9">
+        <v>491520</v>
+      </c>
+      <c r="H75" s="30">
+        <v>41281</v>
+      </c>
+      <c r="I75" s="9">
+        <f t="shared" si="6"/>
+        <v>450239</v>
+      </c>
+      <c r="J75" s="10">
+        <f t="shared" si="7"/>
+        <v>8.3986409505208331E-2</v>
+      </c>
+      <c r="K75" s="43">
+        <f t="shared" si="8"/>
+        <v>330.29715199999998</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="8">
+        <v>72</v>
+      </c>
+      <c r="B76" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C76" s="8">
+        <v>256</v>
+      </c>
+      <c r="D76" s="8">
+        <v>65</v>
+      </c>
+      <c r="E76" s="8">
+        <v>16</v>
+      </c>
+      <c r="F76" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G76" s="9">
+        <v>491520</v>
+      </c>
+      <c r="H76" s="30">
+        <v>41281</v>
+      </c>
+      <c r="I76" s="9">
+        <f t="shared" si="6"/>
+        <v>450239</v>
+      </c>
+      <c r="J76" s="10">
+        <f t="shared" si="7"/>
+        <v>8.3986409505208331E-2</v>
+      </c>
+      <c r="K76" s="43">
+        <f t="shared" si="8"/>
+        <v>330.29715199999998</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="6">
+        <v>73</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C77" s="6">
+        <v>1024</v>
+      </c>
+      <c r="D77" s="6">
+        <v>17</v>
+      </c>
+      <c r="E77" s="6">
         <v>4</v>
       </c>
-      <c r="F41" s="7" t="s">
+      <c r="F77" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G41" s="8">
-        <v>7680</v>
-      </c>
-      <c r="H41" s="31">
-        <v>2</v>
-      </c>
-      <c r="I41" s="8">
-        <f t="shared" si="2"/>
-        <v>7678</v>
-      </c>
-      <c r="J41" s="9">
-        <f t="shared" si="3"/>
-        <v>2.6041666666666666E-4</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="7">
-        <v>38</v>
-      </c>
-      <c r="B42" s="7" t="s">
+      <c r="G77" s="3">
+        <v>491520</v>
+      </c>
+      <c r="H77" s="29">
+        <v>12900</v>
+      </c>
+      <c r="I77" s="3">
+        <f t="shared" si="6"/>
+        <v>478620</v>
+      </c>
+      <c r="J77" s="7">
+        <f t="shared" si="7"/>
+        <v>2.62451171875E-2</v>
+      </c>
+      <c r="K77" s="43">
+        <f t="shared" si="8"/>
+        <v>103.24915200000001</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="6">
+        <v>74</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C78" s="6">
+        <v>1024</v>
+      </c>
+      <c r="D78" s="6">
+        <v>17</v>
+      </c>
+      <c r="E78" s="6">
+        <v>4</v>
+      </c>
+      <c r="F78" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G78" s="3">
+        <v>491520</v>
+      </c>
+      <c r="H78" s="29">
+        <v>10321</v>
+      </c>
+      <c r="I78" s="3">
+        <f t="shared" si="6"/>
+        <v>481199</v>
+      </c>
+      <c r="J78" s="7">
+        <f t="shared" si="7"/>
+        <v>2.0998128255208335E-2</v>
+      </c>
+      <c r="K78" s="43">
+        <f t="shared" si="8"/>
+        <v>82.617152000000004</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="6">
+        <v>75</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C79" s="6">
+        <v>1024</v>
+      </c>
+      <c r="D79" s="6">
+        <v>17</v>
+      </c>
+      <c r="E79" s="6">
+        <v>4</v>
+      </c>
+      <c r="F79" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G79" s="3">
+        <v>491520</v>
+      </c>
+      <c r="H79" s="29">
+        <v>10321</v>
+      </c>
+      <c r="I79" s="3">
+        <f t="shared" si="6"/>
+        <v>481199</v>
+      </c>
+      <c r="J79" s="7">
+        <f t="shared" si="7"/>
+        <v>2.0998128255208335E-2</v>
+      </c>
+      <c r="K79" s="43">
+        <f t="shared" si="8"/>
+        <v>82.617152000000004</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="8">
+        <v>76</v>
+      </c>
+      <c r="B80" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C80" s="8">
+        <v>1024</v>
+      </c>
+      <c r="D80" s="8">
+        <v>17</v>
+      </c>
+      <c r="E80" s="8">
+        <v>8</v>
+      </c>
+      <c r="F80" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G80" s="9">
+        <v>491520</v>
+      </c>
+      <c r="H80" s="30">
+        <v>11610</v>
+      </c>
+      <c r="I80" s="9">
+        <f t="shared" si="6"/>
+        <v>479910</v>
+      </c>
+      <c r="J80" s="10">
+        <f t="shared" si="7"/>
+        <v>2.362060546875E-2</v>
+      </c>
+      <c r="K80" s="43">
+        <f t="shared" si="8"/>
+        <v>92.929152000000002</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="8">
+        <v>77</v>
+      </c>
+      <c r="B81" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C81" s="8">
+        <v>1024</v>
+      </c>
+      <c r="D81" s="8">
+        <v>17</v>
+      </c>
+      <c r="E81" s="8">
+        <v>8</v>
+      </c>
+      <c r="F81" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G81" s="9">
+        <v>491520</v>
+      </c>
+      <c r="H81" s="30">
+        <v>10321</v>
+      </c>
+      <c r="I81" s="9">
+        <f t="shared" si="6"/>
+        <v>481199</v>
+      </c>
+      <c r="J81" s="10">
+        <f t="shared" si="7"/>
+        <v>2.0998128255208335E-2</v>
+      </c>
+      <c r="K81" s="43">
+        <f t="shared" si="8"/>
+        <v>82.617152000000004</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="8">
+        <v>78</v>
+      </c>
+      <c r="B82" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C82" s="8">
+        <v>1024</v>
+      </c>
+      <c r="D82" s="8">
+        <v>17</v>
+      </c>
+      <c r="E82" s="8">
+        <v>8</v>
+      </c>
+      <c r="F82" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G82" s="9">
+        <v>491520</v>
+      </c>
+      <c r="H82" s="30">
+        <v>10321</v>
+      </c>
+      <c r="I82" s="9">
+        <f t="shared" si="6"/>
+        <v>481199</v>
+      </c>
+      <c r="J82" s="10">
+        <f t="shared" si="7"/>
+        <v>2.0998128255208335E-2</v>
+      </c>
+      <c r="K82" s="43">
+        <f t="shared" si="8"/>
+        <v>82.617152000000004</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="6">
+        <v>79</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C83" s="6">
+        <v>1024</v>
+      </c>
+      <c r="D83" s="6">
+        <v>17</v>
+      </c>
+      <c r="E83" s="6">
         <v>16</v>
       </c>
-      <c r="C42" s="7">
-        <v>256</v>
-      </c>
-      <c r="D42" s="7">
-        <v>2</v>
-      </c>
-      <c r="E42" s="7">
-        <v>4</v>
-      </c>
-      <c r="F42" s="7" t="s">
+      <c r="F83" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G83" s="3">
+        <v>491520</v>
+      </c>
+      <c r="H83" s="29">
+        <v>10965</v>
+      </c>
+      <c r="I83" s="3">
+        <f t="shared" si="6"/>
+        <v>480555</v>
+      </c>
+      <c r="J83" s="7">
+        <f t="shared" si="7"/>
+        <v>2.2308349609375E-2</v>
+      </c>
+      <c r="K83" s="43">
+        <f t="shared" si="8"/>
+        <v>87.769152000000005</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="6">
+        <v>80</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C84" s="6">
+        <v>1024</v>
+      </c>
+      <c r="D84" s="6">
+        <v>17</v>
+      </c>
+      <c r="E84" s="6">
+        <v>16</v>
+      </c>
+      <c r="F84" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G42" s="8">
-        <v>7680</v>
-      </c>
-      <c r="H42" s="31">
-        <v>2</v>
-      </c>
-      <c r="I42" s="8">
-        <f t="shared" si="2"/>
-        <v>7678</v>
-      </c>
-      <c r="J42" s="9">
-        <f t="shared" si="3"/>
-        <v>2.6041666666666666E-4</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="7">
-        <v>39</v>
-      </c>
-      <c r="B43" s="7" t="s">
+      <c r="G84" s="3">
+        <v>491520</v>
+      </c>
+      <c r="H84" s="29">
+        <v>10321</v>
+      </c>
+      <c r="I84" s="3">
+        <f t="shared" si="6"/>
+        <v>481199</v>
+      </c>
+      <c r="J84" s="7">
+        <f t="shared" si="7"/>
+        <v>2.0998128255208335E-2</v>
+      </c>
+      <c r="K84" s="43">
+        <f t="shared" si="8"/>
+        <v>82.617152000000004</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="6">
+        <v>81</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C85" s="6">
+        <v>1024</v>
+      </c>
+      <c r="D85" s="6">
+        <v>17</v>
+      </c>
+      <c r="E85" s="6">
         <v>16</v>
       </c>
-      <c r="C43" s="7">
-        <v>256</v>
-      </c>
-      <c r="D43" s="7">
-        <v>2</v>
-      </c>
-      <c r="E43" s="7">
-        <v>4</v>
-      </c>
-      <c r="F43" s="7" t="s">
+      <c r="F85" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G43" s="8">
-        <v>7680</v>
-      </c>
-      <c r="H43" s="31">
-        <v>2</v>
-      </c>
-      <c r="I43" s="8">
-        <f t="shared" si="2"/>
-        <v>7678</v>
-      </c>
-      <c r="J43" s="9">
-        <f t="shared" si="3"/>
-        <v>2.6041666666666666E-4</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="10">
-        <v>40</v>
-      </c>
-      <c r="B44" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C44" s="10">
-        <v>256</v>
-      </c>
-      <c r="D44" s="10">
-        <v>2</v>
-      </c>
-      <c r="E44" s="10">
-        <v>8</v>
-      </c>
-      <c r="F44" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G44" s="11">
-        <v>7680</v>
-      </c>
-      <c r="H44" s="32">
-        <v>2</v>
-      </c>
-      <c r="I44" s="11">
-        <f t="shared" si="2"/>
-        <v>7678</v>
-      </c>
-      <c r="J44" s="12">
-        <f t="shared" si="3"/>
-        <v>2.6041666666666666E-4</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="10">
-        <v>41</v>
-      </c>
-      <c r="B45" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C45" s="10">
-        <v>256</v>
-      </c>
-      <c r="D45" s="10">
-        <v>2</v>
-      </c>
-      <c r="E45" s="10">
-        <v>8</v>
-      </c>
-      <c r="F45" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G45" s="11">
-        <v>7680</v>
-      </c>
-      <c r="H45" s="32">
-        <v>2</v>
-      </c>
-      <c r="I45" s="11">
-        <f t="shared" si="2"/>
-        <v>7678</v>
-      </c>
-      <c r="J45" s="12">
-        <f t="shared" si="3"/>
-        <v>2.6041666666666666E-4</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="10">
-        <v>42</v>
-      </c>
-      <c r="B46" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C46" s="10">
-        <v>256</v>
-      </c>
-      <c r="D46" s="10">
-        <v>2</v>
-      </c>
-      <c r="E46" s="10">
-        <v>8</v>
-      </c>
-      <c r="F46" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G46" s="11">
-        <v>7680</v>
-      </c>
-      <c r="H46" s="32">
-        <v>2</v>
-      </c>
-      <c r="I46" s="11">
-        <f t="shared" si="2"/>
-        <v>7678</v>
-      </c>
-      <c r="J46" s="12">
-        <f t="shared" si="3"/>
-        <v>2.6041666666666666E-4</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="7">
-        <v>43</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C47" s="7">
-        <v>256</v>
-      </c>
-      <c r="D47" s="7">
-        <v>2</v>
-      </c>
-      <c r="E47" s="7">
-        <v>16</v>
-      </c>
-      <c r="F47" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G47" s="8">
-        <v>7680</v>
-      </c>
-      <c r="H47" s="31">
-        <v>2</v>
-      </c>
-      <c r="I47" s="8">
-        <f t="shared" si="2"/>
-        <v>7678</v>
-      </c>
-      <c r="J47" s="9">
-        <f t="shared" si="3"/>
-        <v>2.6041666666666666E-4</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="7">
-        <v>44</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C48" s="7">
-        <v>256</v>
-      </c>
-      <c r="D48" s="7">
-        <v>2</v>
-      </c>
-      <c r="E48" s="7">
-        <v>16</v>
-      </c>
-      <c r="F48" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G48" s="8">
-        <v>7680</v>
-      </c>
-      <c r="H48" s="31">
-        <v>2</v>
-      </c>
-      <c r="I48" s="8">
-        <f t="shared" si="2"/>
-        <v>7678</v>
-      </c>
-      <c r="J48" s="9">
-        <f t="shared" si="3"/>
-        <v>2.6041666666666666E-4</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="7">
-        <v>45</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C49" s="7">
-        <v>256</v>
-      </c>
-      <c r="D49" s="7">
-        <v>2</v>
-      </c>
-      <c r="E49" s="7">
-        <v>16</v>
-      </c>
-      <c r="F49" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G49" s="8">
-        <v>7680</v>
-      </c>
-      <c r="H49" s="31">
-        <v>2</v>
-      </c>
-      <c r="I49" s="8">
-        <f t="shared" si="2"/>
-        <v>7678</v>
-      </c>
-      <c r="J49" s="9">
-        <f t="shared" si="3"/>
-        <v>2.6041666666666666E-4</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="10">
-        <v>46</v>
-      </c>
-      <c r="B50" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C50" s="10">
-        <v>1024</v>
-      </c>
-      <c r="D50" s="10">
-        <v>1</v>
-      </c>
-      <c r="E50" s="10">
-        <v>4</v>
-      </c>
-      <c r="F50" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G50" s="11">
-        <v>7680</v>
-      </c>
-      <c r="H50" s="32">
-        <v>1</v>
-      </c>
-      <c r="I50" s="11">
-        <f t="shared" si="2"/>
-        <v>7679</v>
-      </c>
-      <c r="J50" s="12">
-        <f t="shared" si="3"/>
-        <v>1.3020833333333333E-4</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="10">
-        <v>47</v>
-      </c>
-      <c r="B51" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C51" s="10">
-        <v>1024</v>
-      </c>
-      <c r="D51" s="10">
-        <v>1</v>
-      </c>
-      <c r="E51" s="10">
-        <v>4</v>
-      </c>
-      <c r="F51" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G51" s="11">
-        <v>7680</v>
-      </c>
-      <c r="H51" s="32">
-        <v>1</v>
-      </c>
-      <c r="I51" s="11">
-        <f t="shared" si="2"/>
-        <v>7679</v>
-      </c>
-      <c r="J51" s="12">
-        <f t="shared" si="3"/>
-        <v>1.3020833333333333E-4</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="10">
-        <v>48</v>
-      </c>
-      <c r="B52" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C52" s="10">
-        <v>1024</v>
-      </c>
-      <c r="D52" s="10">
-        <v>1</v>
-      </c>
-      <c r="E52" s="10">
-        <v>4</v>
-      </c>
-      <c r="F52" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G52" s="11">
-        <v>7680</v>
-      </c>
-      <c r="H52" s="32">
-        <v>1</v>
-      </c>
-      <c r="I52" s="11">
-        <f t="shared" si="2"/>
-        <v>7679</v>
-      </c>
-      <c r="J52" s="12">
-        <f t="shared" si="3"/>
-        <v>1.3020833333333333E-4</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="7">
-        <v>49</v>
-      </c>
-      <c r="B53" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C53" s="7">
-        <v>1024</v>
-      </c>
-      <c r="D53" s="7">
-        <v>1</v>
-      </c>
-      <c r="E53" s="7">
-        <v>8</v>
-      </c>
-      <c r="F53" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G53" s="8">
-        <v>7680</v>
-      </c>
-      <c r="H53" s="31">
-        <v>1</v>
-      </c>
-      <c r="I53" s="8">
-        <f t="shared" si="2"/>
-        <v>7679</v>
-      </c>
-      <c r="J53" s="9">
-        <f t="shared" si="3"/>
-        <v>1.3020833333333333E-4</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="7">
-        <v>50</v>
-      </c>
-      <c r="B54" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C54" s="7">
-        <v>1024</v>
-      </c>
-      <c r="D54" s="7">
-        <v>1</v>
-      </c>
-      <c r="E54" s="7">
-        <v>8</v>
-      </c>
-      <c r="F54" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G54" s="8">
-        <v>7680</v>
-      </c>
-      <c r="H54" s="31">
-        <v>1</v>
-      </c>
-      <c r="I54" s="8">
-        <f t="shared" si="2"/>
-        <v>7679</v>
-      </c>
-      <c r="J54" s="9">
-        <f t="shared" si="3"/>
-        <v>1.3020833333333333E-4</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="7">
-        <v>51</v>
-      </c>
-      <c r="B55" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C55" s="7">
-        <v>1024</v>
-      </c>
-      <c r="D55" s="7">
-        <v>1</v>
-      </c>
-      <c r="E55" s="7">
-        <v>8</v>
-      </c>
-      <c r="F55" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G55" s="8">
-        <v>7680</v>
-      </c>
-      <c r="H55" s="31">
-        <v>1</v>
-      </c>
-      <c r="I55" s="8">
-        <f t="shared" si="2"/>
-        <v>7679</v>
-      </c>
-      <c r="J55" s="9">
-        <f t="shared" si="3"/>
-        <v>1.3020833333333333E-4</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="10">
-        <v>52</v>
-      </c>
-      <c r="B56" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C56" s="10">
-        <v>1024</v>
-      </c>
-      <c r="D56" s="10">
-        <v>1</v>
-      </c>
-      <c r="E56" s="10">
-        <v>16</v>
-      </c>
-      <c r="F56" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G56" s="11">
-        <v>7680</v>
-      </c>
-      <c r="H56" s="32">
-        <v>1</v>
-      </c>
-      <c r="I56" s="11">
-        <f t="shared" si="2"/>
-        <v>7679</v>
-      </c>
-      <c r="J56" s="12">
-        <f t="shared" si="3"/>
-        <v>1.3020833333333333E-4</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="22">
-        <v>53</v>
-      </c>
-      <c r="B57" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C57" s="22">
-        <v>1024</v>
-      </c>
-      <c r="D57" s="22">
-        <v>1</v>
-      </c>
-      <c r="E57" s="22">
-        <v>16</v>
-      </c>
-      <c r="F57" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="G57" s="23">
-        <v>7680</v>
-      </c>
-      <c r="H57" s="36">
-        <v>1</v>
-      </c>
-      <c r="I57" s="23">
-        <f t="shared" si="2"/>
-        <v>7679</v>
-      </c>
-      <c r="J57" s="24">
-        <f t="shared" si="3"/>
-        <v>1.3020833333333333E-4</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="28">
-        <v>54</v>
-      </c>
-      <c r="B58" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C58" s="28">
-        <v>1024</v>
-      </c>
-      <c r="D58" s="28">
-        <v>1</v>
-      </c>
-      <c r="E58" s="28">
-        <v>16</v>
-      </c>
-      <c r="F58" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="G58" s="29">
-        <v>7680</v>
-      </c>
-      <c r="H58" s="37">
-        <v>1</v>
-      </c>
-      <c r="I58" s="29">
-        <f t="shared" si="2"/>
-        <v>7679</v>
-      </c>
-      <c r="J58" s="30">
-        <f t="shared" si="3"/>
-        <v>1.3020833333333333E-4</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="25">
-        <v>55</v>
-      </c>
-      <c r="B59" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="C59" s="25">
-        <v>64</v>
-      </c>
-      <c r="D59" s="25">
-        <v>259</v>
-      </c>
-      <c r="E59" s="25">
-        <v>4</v>
-      </c>
-      <c r="F59" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="G59" s="26">
+      <c r="G85" s="3">
         <v>491520</v>
       </c>
-      <c r="H59" s="38">
-        <v>104320</v>
-      </c>
-      <c r="I59" s="26">
-        <f t="shared" si="2"/>
-        <v>387200</v>
-      </c>
-      <c r="J59" s="27">
-        <f t="shared" si="3"/>
-        <v>0.21223958333333334</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="7">
-        <v>56</v>
-      </c>
-      <c r="B60" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C60" s="7">
-        <v>64</v>
-      </c>
-      <c r="D60" s="7">
-        <v>259</v>
-      </c>
-      <c r="E60" s="7">
-        <v>4</v>
-      </c>
-      <c r="F60" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G60" s="8">
-        <v>491520</v>
-      </c>
-      <c r="H60" s="31">
-        <v>85760</v>
-      </c>
-      <c r="I60" s="8">
-        <f t="shared" si="2"/>
-        <v>405760</v>
-      </c>
-      <c r="J60" s="9">
-        <f t="shared" si="3"/>
-        <v>0.17447916666666666</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="7">
-        <v>57</v>
-      </c>
-      <c r="B61" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C61" s="7">
-        <v>64</v>
-      </c>
-      <c r="D61" s="7">
-        <v>259</v>
-      </c>
-      <c r="E61" s="7">
-        <v>4</v>
-      </c>
-      <c r="F61" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G61" s="8">
-        <v>491520</v>
-      </c>
-      <c r="H61" s="31">
-        <v>85760</v>
-      </c>
-      <c r="I61" s="8">
-        <f t="shared" si="2"/>
-        <v>405760</v>
-      </c>
-      <c r="J61" s="9">
-        <f t="shared" si="3"/>
-        <v>0.17447916666666666</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="10">
-        <v>58</v>
-      </c>
-      <c r="B62" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C62" s="10">
-        <v>64</v>
-      </c>
-      <c r="D62" s="10">
-        <v>259</v>
-      </c>
-      <c r="E62" s="10">
-        <v>8</v>
-      </c>
-      <c r="F62" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G62" s="11">
-        <v>491520</v>
-      </c>
-      <c r="H62" s="32">
-        <v>93760</v>
-      </c>
-      <c r="I62" s="11">
-        <f t="shared" si="2"/>
-        <v>397760</v>
-      </c>
-      <c r="J62" s="12">
-        <f t="shared" si="3"/>
-        <v>0.19075520833333334</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="10">
-        <v>59</v>
-      </c>
-      <c r="B63" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C63" s="10">
-        <v>64</v>
-      </c>
-      <c r="D63" s="10">
-        <v>259</v>
-      </c>
-      <c r="E63" s="10">
-        <v>8</v>
-      </c>
-      <c r="F63" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G63" s="11">
-        <v>491520</v>
-      </c>
-      <c r="H63" s="32">
-        <v>84481</v>
-      </c>
-      <c r="I63" s="11">
-        <f t="shared" si="2"/>
-        <v>407039</v>
-      </c>
-      <c r="J63" s="12">
-        <f t="shared" si="3"/>
-        <v>0.17187703450520833</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="10">
-        <v>60</v>
-      </c>
-      <c r="B64" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C64" s="10">
-        <v>64</v>
-      </c>
-      <c r="D64" s="10">
-        <v>259</v>
-      </c>
-      <c r="E64" s="10">
-        <v>8</v>
-      </c>
-      <c r="F64" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G64" s="11">
-        <v>491520</v>
-      </c>
-      <c r="H64" s="32">
-        <v>84481</v>
-      </c>
-      <c r="I64" s="11">
-        <f t="shared" si="2"/>
-        <v>407039</v>
-      </c>
-      <c r="J64" s="12">
-        <f t="shared" si="3"/>
-        <v>0.17187703450520833</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="7">
-        <v>61</v>
-      </c>
-      <c r="B65" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C65" s="7">
-        <v>64</v>
-      </c>
-      <c r="D65" s="7">
-        <v>259</v>
-      </c>
-      <c r="E65" s="7">
-        <v>16</v>
-      </c>
-      <c r="F65" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G65" s="8">
-        <v>491520</v>
-      </c>
-      <c r="H65" s="31">
-        <v>88480</v>
-      </c>
-      <c r="I65" s="8">
-        <f t="shared" si="2"/>
-        <v>403040</v>
-      </c>
-      <c r="J65" s="9">
-        <f t="shared" si="3"/>
-        <v>0.18001302083333334</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="7">
-        <v>62</v>
-      </c>
-      <c r="B66" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C66" s="7">
-        <v>64</v>
-      </c>
-      <c r="D66" s="7">
-        <v>259</v>
-      </c>
-      <c r="E66" s="7">
-        <v>16</v>
-      </c>
-      <c r="F66" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G66" s="8">
-        <v>491520</v>
-      </c>
-      <c r="H66" s="31">
-        <v>84481</v>
-      </c>
-      <c r="I66" s="8">
-        <f t="shared" si="2"/>
-        <v>407039</v>
-      </c>
-      <c r="J66" s="9">
-        <f t="shared" si="3"/>
-        <v>0.17187703450520833</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="7">
-        <v>63</v>
-      </c>
-      <c r="B67" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C67" s="7">
-        <v>64</v>
-      </c>
-      <c r="D67" s="7">
-        <v>259</v>
-      </c>
-      <c r="E67" s="7">
-        <v>16</v>
-      </c>
-      <c r="F67" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G67" s="8">
-        <v>491520</v>
-      </c>
-      <c r="H67" s="31">
-        <v>84481</v>
-      </c>
-      <c r="I67" s="8">
-        <f t="shared" si="2"/>
-        <v>407039</v>
-      </c>
-      <c r="J67" s="9">
-        <f t="shared" si="3"/>
-        <v>0.17187703450520833</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="10">
-        <v>64</v>
-      </c>
-      <c r="B68" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C68" s="10">
-        <v>256</v>
-      </c>
-      <c r="D68" s="10">
-        <v>65</v>
-      </c>
-      <c r="E68" s="10">
-        <v>4</v>
-      </c>
-      <c r="F68" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G68" s="11">
-        <v>491520</v>
-      </c>
-      <c r="H68" s="32">
-        <v>51600</v>
-      </c>
-      <c r="I68" s="11">
-        <f t="shared" si="2"/>
-        <v>439920</v>
-      </c>
-      <c r="J68" s="12">
-        <f t="shared" si="3"/>
-        <v>0.10498046875</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="10">
-        <v>65</v>
-      </c>
-      <c r="B69" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C69" s="10">
-        <v>256</v>
-      </c>
-      <c r="D69" s="10">
-        <v>65</v>
-      </c>
-      <c r="E69" s="10">
-        <v>4</v>
-      </c>
-      <c r="F69" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G69" s="11">
-        <v>491520</v>
-      </c>
-      <c r="H69" s="32">
-        <v>41281</v>
-      </c>
-      <c r="I69" s="11">
-        <f t="shared" ref="I69:I100" si="4">G69-H69</f>
-        <v>450239</v>
-      </c>
-      <c r="J69" s="12">
-        <f t="shared" ref="J69:J85" si="5">H69/G69</f>
-        <v>8.3986409505208331E-2</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="10">
-        <v>66</v>
-      </c>
-      <c r="B70" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C70" s="10">
-        <v>256</v>
-      </c>
-      <c r="D70" s="10">
-        <v>65</v>
-      </c>
-      <c r="E70" s="10">
-        <v>4</v>
-      </c>
-      <c r="F70" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G70" s="11">
-        <v>491520</v>
-      </c>
-      <c r="H70" s="32">
-        <v>41281</v>
-      </c>
-      <c r="I70" s="11">
-        <f t="shared" si="4"/>
-        <v>450239</v>
-      </c>
-      <c r="J70" s="12">
-        <f t="shared" si="5"/>
-        <v>8.3986409505208331E-2</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="7">
-        <v>67</v>
-      </c>
-      <c r="B71" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C71" s="7">
-        <v>256</v>
-      </c>
-      <c r="D71" s="7">
-        <v>65</v>
-      </c>
-      <c r="E71" s="7">
-        <v>8</v>
-      </c>
-      <c r="F71" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G71" s="8">
-        <v>491520</v>
-      </c>
-      <c r="H71" s="31">
-        <v>46440</v>
-      </c>
-      <c r="I71" s="8">
-        <f t="shared" si="4"/>
-        <v>445080</v>
-      </c>
-      <c r="J71" s="9">
-        <f t="shared" si="5"/>
-        <v>9.4482421875E-2</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="7">
-        <v>68</v>
-      </c>
-      <c r="B72" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C72" s="7">
-        <v>256</v>
-      </c>
-      <c r="D72" s="7">
-        <v>65</v>
-      </c>
-      <c r="E72" s="7">
-        <v>8</v>
-      </c>
-      <c r="F72" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G72" s="8">
-        <v>491520</v>
-      </c>
-      <c r="H72" s="31">
-        <v>41281</v>
-      </c>
-      <c r="I72" s="8">
-        <f t="shared" si="4"/>
-        <v>450239</v>
-      </c>
-      <c r="J72" s="9">
-        <f t="shared" si="5"/>
-        <v>8.3986409505208331E-2</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="7">
-        <v>69</v>
-      </c>
-      <c r="B73" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C73" s="7">
-        <v>256</v>
-      </c>
-      <c r="D73" s="7">
-        <v>65</v>
-      </c>
-      <c r="E73" s="7">
-        <v>8</v>
-      </c>
-      <c r="F73" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G73" s="8">
-        <v>491520</v>
-      </c>
-      <c r="H73" s="31">
-        <v>41281</v>
-      </c>
-      <c r="I73" s="8">
-        <f t="shared" si="4"/>
-        <v>450239</v>
-      </c>
-      <c r="J73" s="9">
-        <f t="shared" si="5"/>
-        <v>8.3986409505208331E-2</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="10">
-        <v>70</v>
-      </c>
-      <c r="B74" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C74" s="10">
-        <v>256</v>
-      </c>
-      <c r="D74" s="10">
-        <v>65</v>
-      </c>
-      <c r="E74" s="10">
-        <v>16</v>
-      </c>
-      <c r="F74" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G74" s="11">
-        <v>491520</v>
-      </c>
-      <c r="H74" s="32">
-        <v>43860</v>
-      </c>
-      <c r="I74" s="11">
-        <f t="shared" si="4"/>
-        <v>447660</v>
-      </c>
-      <c r="J74" s="12">
-        <f t="shared" si="5"/>
-        <v>8.92333984375E-2</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="10">
-        <v>71</v>
-      </c>
-      <c r="B75" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C75" s="10">
-        <v>256</v>
-      </c>
-      <c r="D75" s="10">
-        <v>65</v>
-      </c>
-      <c r="E75" s="10">
-        <v>16</v>
-      </c>
-      <c r="F75" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G75" s="11">
-        <v>491520</v>
-      </c>
-      <c r="H75" s="32">
-        <v>41281</v>
-      </c>
-      <c r="I75" s="11">
-        <f t="shared" si="4"/>
-        <v>450239</v>
-      </c>
-      <c r="J75" s="12">
-        <f t="shared" si="5"/>
-        <v>8.3986409505208331E-2</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="10">
-        <v>72</v>
-      </c>
-      <c r="B76" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C76" s="10">
-        <v>256</v>
-      </c>
-      <c r="D76" s="10">
-        <v>65</v>
-      </c>
-      <c r="E76" s="10">
-        <v>16</v>
-      </c>
-      <c r="F76" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G76" s="11">
-        <v>491520</v>
-      </c>
-      <c r="H76" s="32">
-        <v>41281</v>
-      </c>
-      <c r="I76" s="11">
-        <f t="shared" si="4"/>
-        <v>450239</v>
-      </c>
-      <c r="J76" s="12">
-        <f t="shared" si="5"/>
-        <v>8.3986409505208331E-2</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="7">
-        <v>73</v>
-      </c>
-      <c r="B77" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C77" s="7">
-        <v>1024</v>
-      </c>
-      <c r="D77" s="7">
-        <v>17</v>
-      </c>
-      <c r="E77" s="7">
-        <v>4</v>
-      </c>
-      <c r="F77" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G77" s="8">
-        <v>491520</v>
-      </c>
-      <c r="H77" s="31">
-        <v>12900</v>
-      </c>
-      <c r="I77" s="8">
-        <f t="shared" si="4"/>
-        <v>478620</v>
-      </c>
-      <c r="J77" s="9">
-        <f t="shared" si="5"/>
-        <v>2.62451171875E-2</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="7">
-        <v>74</v>
-      </c>
-      <c r="B78" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C78" s="7">
-        <v>1024</v>
-      </c>
-      <c r="D78" s="7">
-        <v>17</v>
-      </c>
-      <c r="E78" s="7">
-        <v>4</v>
-      </c>
-      <c r="F78" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G78" s="8">
-        <v>491520</v>
-      </c>
-      <c r="H78" s="31">
+      <c r="H85" s="29">
         <v>10321</v>
       </c>
-      <c r="I78" s="8">
-        <f t="shared" si="4"/>
+      <c r="I85" s="3">
+        <f t="shared" si="6"/>
         <v>481199</v>
       </c>
-      <c r="J78" s="9">
-        <f t="shared" si="5"/>
+      <c r="J85" s="7">
+        <f t="shared" si="7"/>
         <v>2.0998128255208335E-2</v>
       </c>
-    </row>
-    <row r="79" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="7">
-        <v>75</v>
-      </c>
-      <c r="B79" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C79" s="7">
-        <v>1024</v>
-      </c>
-      <c r="D79" s="7">
-        <v>17</v>
-      </c>
-      <c r="E79" s="7">
-        <v>4</v>
-      </c>
-      <c r="F79" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G79" s="8">
-        <v>491520</v>
-      </c>
-      <c r="H79" s="31">
-        <v>10321</v>
-      </c>
-      <c r="I79" s="8">
-        <f t="shared" si="4"/>
-        <v>481199</v>
-      </c>
-      <c r="J79" s="9">
-        <f t="shared" si="5"/>
-        <v>2.0998128255208335E-2</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="10">
-        <v>76</v>
-      </c>
-      <c r="B80" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C80" s="10">
-        <v>1024</v>
-      </c>
-      <c r="D80" s="10">
-        <v>17</v>
-      </c>
-      <c r="E80" s="10">
-        <v>8</v>
-      </c>
-      <c r="F80" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G80" s="11">
-        <v>491520</v>
-      </c>
-      <c r="H80" s="32">
-        <v>11610</v>
-      </c>
-      <c r="I80" s="11">
-        <f t="shared" si="4"/>
-        <v>479910</v>
-      </c>
-      <c r="J80" s="12">
-        <f t="shared" si="5"/>
-        <v>2.362060546875E-2</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="10">
-        <v>77</v>
-      </c>
-      <c r="B81" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C81" s="10">
-        <v>1024</v>
-      </c>
-      <c r="D81" s="10">
-        <v>17</v>
-      </c>
-      <c r="E81" s="10">
-        <v>8</v>
-      </c>
-      <c r="F81" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G81" s="11">
-        <v>491520</v>
-      </c>
-      <c r="H81" s="32">
-        <v>10321</v>
-      </c>
-      <c r="I81" s="11">
-        <f t="shared" si="4"/>
-        <v>481199</v>
-      </c>
-      <c r="J81" s="12">
-        <f t="shared" si="5"/>
-        <v>2.0998128255208335E-2</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="10">
-        <v>78</v>
-      </c>
-      <c r="B82" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C82" s="10">
-        <v>1024</v>
-      </c>
-      <c r="D82" s="10">
-        <v>17</v>
-      </c>
-      <c r="E82" s="10">
-        <v>8</v>
-      </c>
-      <c r="F82" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G82" s="11">
-        <v>491520</v>
-      </c>
-      <c r="H82" s="32">
-        <v>10321</v>
-      </c>
-      <c r="I82" s="11">
-        <f t="shared" si="4"/>
-        <v>481199</v>
-      </c>
-      <c r="J82" s="12">
-        <f t="shared" si="5"/>
-        <v>2.0998128255208335E-2</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="7">
-        <v>79</v>
-      </c>
-      <c r="B83" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C83" s="7">
-        <v>1024</v>
-      </c>
-      <c r="D83" s="7">
-        <v>17</v>
-      </c>
-      <c r="E83" s="7">
-        <v>16</v>
-      </c>
-      <c r="F83" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G83" s="8">
-        <v>491520</v>
-      </c>
-      <c r="H83" s="31">
-        <v>10965</v>
-      </c>
-      <c r="I83" s="8">
-        <f t="shared" si="4"/>
-        <v>480555</v>
-      </c>
-      <c r="J83" s="9">
-        <f t="shared" si="5"/>
-        <v>2.2308349609375E-2</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="7">
-        <v>80</v>
-      </c>
-      <c r="B84" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C84" s="7">
-        <v>1024</v>
-      </c>
-      <c r="D84" s="7">
-        <v>17</v>
-      </c>
-      <c r="E84" s="7">
-        <v>16</v>
-      </c>
-      <c r="F84" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G84" s="8">
-        <v>491520</v>
-      </c>
-      <c r="H84" s="31">
-        <v>10321</v>
-      </c>
-      <c r="I84" s="8">
-        <f t="shared" si="4"/>
-        <v>481199</v>
-      </c>
-      <c r="J84" s="9">
-        <f t="shared" si="5"/>
-        <v>2.0998128255208335E-2</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="7">
-        <v>81</v>
-      </c>
-      <c r="B85" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C85" s="7">
-        <v>1024</v>
-      </c>
-      <c r="D85" s="7">
-        <v>17</v>
-      </c>
-      <c r="E85" s="7">
-        <v>16</v>
-      </c>
-      <c r="F85" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G85" s="8">
-        <v>491520</v>
-      </c>
-      <c r="H85" s="31">
-        <v>10321</v>
-      </c>
-      <c r="I85" s="8">
-        <f t="shared" si="4"/>
-        <v>481199</v>
-      </c>
-      <c r="J85" s="9">
-        <f t="shared" si="5"/>
-        <v>2.0998128255208335E-2</v>
+      <c r="K85" s="43">
+        <f t="shared" si="8"/>
+        <v>82.617152000000004</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J85" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A4:K85" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8596,21 +8927,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="26" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="40" t="s">
+      <c r="B3" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="41" t="s">
+      <c r="C3" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="40">
+      <c r="D3" s="38">
         <v>64</v>
       </c>
     </row>
@@ -8629,7 +8960,7 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="42">
+      <c r="A5" s="40">
         <v>4</v>
       </c>
       <c r="B5" s="3">
@@ -8646,24 +8977,24 @@
       </c>
     </row>
     <row r="6" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="43">
+      <c r="A6" s="41">
         <v>8</v>
       </c>
-      <c r="B6" s="44">
+      <c r="B6" s="42">
         <f>Datos!H8</f>
         <v>2</v>
       </c>
-      <c r="C6" s="44">
+      <c r="C6" s="42">
         <f>Datos!H9</f>
         <v>2</v>
       </c>
-      <c r="D6" s="44">
+      <c r="D6" s="42">
         <f>Datos!H10</f>
         <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="42">
+      <c r="A7" s="40">
         <v>16</v>
       </c>
       <c r="B7" s="3">
@@ -8679,83 +9010,17 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-    </row>
     <row r="19" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="39" t="s">
+      <c r="A19" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="40" t="s">
+      <c r="B19" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="41" t="s">
+      <c r="C19" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="D19" s="40">
+      <c r="D19" s="38">
         <v>256</v>
       </c>
     </row>
@@ -8774,7 +9039,7 @@
       </c>
     </row>
     <row r="21" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="42">
+      <c r="A21" s="40">
         <v>4</v>
       </c>
       <c r="B21" s="3">
@@ -8791,24 +9056,24 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="43">
+      <c r="A22" s="41">
         <v>8</v>
       </c>
-      <c r="B22" s="44">
+      <c r="B22" s="42">
         <f>Datos!H17</f>
         <v>1</v>
       </c>
-      <c r="C22" s="44">
+      <c r="C22" s="42">
         <f>Datos!H18</f>
         <v>1</v>
       </c>
-      <c r="D22" s="44">
+      <c r="D22" s="42">
         <f>Datos!H19</f>
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="42">
+      <c r="A23" s="40">
         <v>16</v>
       </c>
       <c r="B23" s="3">
@@ -8824,83 +9089,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="4"/>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="4"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="4"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="4"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="4"/>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="4"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-    </row>
     <row r="35" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="39" t="s">
+      <c r="A35" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="B35" s="40" t="s">
+      <c r="B35" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="C35" s="41" t="s">
+      <c r="C35" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="D35" s="40">
+      <c r="D35" s="38">
         <v>1024</v>
       </c>
     </row>
@@ -8919,7 +9118,7 @@
       </c>
     </row>
     <row r="37" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="42">
+      <c r="A37" s="40">
         <v>4</v>
       </c>
       <c r="B37" s="3">
@@ -8936,24 +9135,24 @@
       </c>
     </row>
     <row r="38" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="43">
+      <c r="A38" s="41">
         <v>8</v>
       </c>
-      <c r="B38" s="44">
+      <c r="B38" s="42">
         <f>Datos!H26</f>
         <v>1</v>
       </c>
-      <c r="C38" s="44">
+      <c r="C38" s="42">
         <f>Datos!H27</f>
         <v>1</v>
       </c>
-      <c r="D38" s="44">
+      <c r="D38" s="42">
         <f>Datos!H28</f>
         <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="42">
+      <c r="A39" s="40">
         <v>16</v>
       </c>
       <c r="B39" s="3">
@@ -8969,83 +9168,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A40" s="4"/>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A41" s="4"/>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="4"/>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43" s="4"/>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" s="4"/>
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" s="4"/>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="4"/>
-      <c r="B46" s="4"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A47" s="4"/>
-      <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="4"/>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A48" s="4"/>
-      <c r="B48" s="4"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="4"/>
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="4"/>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="4"/>
-      <c r="B50" s="4"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="4"/>
-    </row>
     <row r="51" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="39" t="s">
+      <c r="A51" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="B51" s="40" t="s">
+      <c r="B51" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="C51" s="41" t="s">
+      <c r="C51" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="D51" s="40">
+      <c r="D51" s="38">
         <v>64</v>
       </c>
     </row>
@@ -9064,7 +9197,7 @@
       </c>
     </row>
     <row r="53" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="42">
+      <c r="A53" s="40">
         <v>4</v>
       </c>
       <c r="B53" s="3">
@@ -9081,24 +9214,24 @@
       </c>
     </row>
     <row r="54" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="43">
+      <c r="A54" s="41">
         <v>8</v>
       </c>
-      <c r="B54" s="44">
+      <c r="B54" s="42">
         <f>Datos!H35</f>
         <v>5</v>
       </c>
-      <c r="C54" s="44">
+      <c r="C54" s="42">
         <f>Datos!H36</f>
         <v>5</v>
       </c>
-      <c r="D54" s="44">
+      <c r="D54" s="42">
         <f>Datos!H37</f>
         <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="42">
+      <c r="A55" s="40">
         <v>16</v>
       </c>
       <c r="B55" s="3">
@@ -9114,83 +9247,17 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" s="4"/>
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A57" s="4"/>
-      <c r="B57" s="4"/>
-      <c r="C57" s="4"/>
-      <c r="D57" s="4"/>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A58" s="4"/>
-      <c r="B58" s="4"/>
-      <c r="C58" s="4"/>
-      <c r="D58" s="4"/>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A59" s="4"/>
-      <c r="B59" s="4"/>
-      <c r="C59" s="4"/>
-      <c r="D59" s="4"/>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A60" s="4"/>
-      <c r="B60" s="4"/>
-      <c r="C60" s="4"/>
-      <c r="D60" s="4"/>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A61" s="4"/>
-      <c r="B61" s="4"/>
-      <c r="C61" s="4"/>
-      <c r="D61" s="4"/>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A62" s="4"/>
-      <c r="B62" s="4"/>
-      <c r="C62" s="4"/>
-      <c r="D62" s="4"/>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A63" s="4"/>
-      <c r="B63" s="4"/>
-      <c r="C63" s="4"/>
-      <c r="D63" s="4"/>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A64" s="4"/>
-      <c r="B64" s="4"/>
-      <c r="C64" s="4"/>
-      <c r="D64" s="4"/>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A65" s="4"/>
-      <c r="B65" s="4"/>
-      <c r="C65" s="4"/>
-      <c r="D65" s="4"/>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A66" s="4"/>
-      <c r="B66" s="4"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="4"/>
-    </row>
     <row r="67" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="39" t="s">
+      <c r="A67" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="B67" s="40" t="s">
+      <c r="B67" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="C67" s="41" t="s">
+      <c r="C67" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="D67" s="40">
+      <c r="D67" s="38">
         <v>256</v>
       </c>
     </row>
@@ -9209,7 +9276,7 @@
       </c>
     </row>
     <row r="69" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="42">
+      <c r="A69" s="40">
         <v>4</v>
       </c>
       <c r="B69" s="3">
@@ -9226,24 +9293,24 @@
       </c>
     </row>
     <row r="70" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="43">
+      <c r="A70" s="41">
         <v>8</v>
       </c>
-      <c r="B70" s="44">
+      <c r="B70" s="42">
         <f>Datos!H44</f>
         <v>2</v>
       </c>
-      <c r="C70" s="44">
+      <c r="C70" s="42">
         <f>Datos!H45</f>
         <v>2</v>
       </c>
-      <c r="D70" s="44">
+      <c r="D70" s="42">
         <f>Datos!H46</f>
         <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="42">
+      <c r="A71" s="40">
         <v>16</v>
       </c>
       <c r="B71" s="3">
@@ -9259,83 +9326,17 @@
         <v>2</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A72" s="4"/>
-      <c r="B72" s="4"/>
-      <c r="C72" s="4"/>
-      <c r="D72" s="4"/>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A73" s="4"/>
-      <c r="B73" s="4"/>
-      <c r="C73" s="4"/>
-      <c r="D73" s="4"/>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A74" s="4"/>
-      <c r="B74" s="4"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="4"/>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A75" s="4"/>
-      <c r="B75" s="4"/>
-      <c r="C75" s="4"/>
-      <c r="D75" s="4"/>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A76" s="4"/>
-      <c r="B76" s="4"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="4"/>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A77" s="4"/>
-      <c r="B77" s="4"/>
-      <c r="C77" s="4"/>
-      <c r="D77" s="4"/>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A78" s="4"/>
-      <c r="B78" s="4"/>
-      <c r="C78" s="4"/>
-      <c r="D78" s="4"/>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A79" s="4"/>
-      <c r="B79" s="4"/>
-      <c r="C79" s="4"/>
-      <c r="D79" s="4"/>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A80" s="4"/>
-      <c r="B80" s="4"/>
-      <c r="C80" s="4"/>
-      <c r="D80" s="4"/>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A81" s="4"/>
-      <c r="B81" s="4"/>
-      <c r="C81" s="4"/>
-      <c r="D81" s="4"/>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A82" s="4"/>
-      <c r="B82" s="4"/>
-      <c r="C82" s="4"/>
-      <c r="D82" s="4"/>
-    </row>
     <row r="83" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="39" t="s">
+      <c r="A83" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="B83" s="40" t="s">
+      <c r="B83" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="C83" s="41" t="s">
+      <c r="C83" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="D83" s="40">
+      <c r="D83" s="38">
         <v>1024</v>
       </c>
     </row>
@@ -9354,7 +9355,7 @@
       </c>
     </row>
     <row r="85" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="42">
+      <c r="A85" s="40">
         <v>4</v>
       </c>
       <c r="B85" s="3">
@@ -9371,24 +9372,24 @@
       </c>
     </row>
     <row r="86" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="43">
+      <c r="A86" s="41">
         <v>8</v>
       </c>
-      <c r="B86" s="44">
+      <c r="B86" s="42">
         <f>Datos!H53</f>
         <v>1</v>
       </c>
-      <c r="C86" s="44">
+      <c r="C86" s="42">
         <f>Datos!H54</f>
         <v>1</v>
       </c>
-      <c r="D86" s="44">
+      <c r="D86" s="42">
         <f>Datos!H55</f>
         <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="42">
+      <c r="A87" s="40">
         <v>16</v>
       </c>
       <c r="B87" s="3">
@@ -9404,83 +9405,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A88" s="4"/>
-      <c r="B88" s="4"/>
-      <c r="C88" s="4"/>
-      <c r="D88" s="4"/>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A89" s="4"/>
-      <c r="B89" s="4"/>
-      <c r="C89" s="4"/>
-      <c r="D89" s="4"/>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A90" s="4"/>
-      <c r="B90" s="4"/>
-      <c r="C90" s="4"/>
-      <c r="D90" s="4"/>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A91" s="4"/>
-      <c r="B91" s="4"/>
-      <c r="C91" s="4"/>
-      <c r="D91" s="4"/>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A92" s="4"/>
-      <c r="B92" s="4"/>
-      <c r="C92" s="4"/>
-      <c r="D92" s="4"/>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A93" s="4"/>
-      <c r="B93" s="4"/>
-      <c r="C93" s="4"/>
-      <c r="D93" s="4"/>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A94" s="4"/>
-      <c r="B94" s="4"/>
-      <c r="C94" s="4"/>
-      <c r="D94" s="4"/>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A95" s="4"/>
-      <c r="B95" s="4"/>
-      <c r="C95" s="4"/>
-      <c r="D95" s="4"/>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A96" s="4"/>
-      <c r="B96" s="4"/>
-      <c r="C96" s="4"/>
-      <c r="D96" s="4"/>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A97" s="4"/>
-      <c r="B97" s="4"/>
-      <c r="C97" s="4"/>
-      <c r="D97" s="4"/>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A98" s="4"/>
-      <c r="B98" s="4"/>
-      <c r="C98" s="4"/>
-      <c r="D98" s="4"/>
-    </row>
     <row r="99" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="39" t="s">
+      <c r="A99" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="B99" s="40" t="s">
+      <c r="B99" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="C99" s="41" t="s">
+      <c r="C99" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="D99" s="40">
+      <c r="D99" s="38">
         <v>64</v>
       </c>
     </row>
@@ -9499,7 +9434,7 @@
       </c>
     </row>
     <row r="101" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="42">
+      <c r="A101" s="40">
         <v>4</v>
       </c>
       <c r="B101" s="3">
@@ -9516,24 +9451,24 @@
       </c>
     </row>
     <row r="102" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="43">
+      <c r="A102" s="41">
         <v>8</v>
       </c>
-      <c r="B102" s="44">
+      <c r="B102" s="42">
         <f>Datos!H62</f>
         <v>93760</v>
       </c>
-      <c r="C102" s="44">
+      <c r="C102" s="42">
         <f>Datos!H63</f>
         <v>84481</v>
       </c>
-      <c r="D102" s="44">
+      <c r="D102" s="42">
         <f>Datos!H64</f>
         <v>84481</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="42">
+      <c r="A103" s="40">
         <v>16</v>
       </c>
       <c r="B103" s="3">
@@ -9549,83 +9484,17 @@
         <v>84481</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A104" s="4"/>
-      <c r="B104" s="4"/>
-      <c r="C104" s="4"/>
-      <c r="D104" s="4"/>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A105" s="4"/>
-      <c r="B105" s="4"/>
-      <c r="C105" s="4"/>
-      <c r="D105" s="4"/>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A106" s="4"/>
-      <c r="B106" s="4"/>
-      <c r="C106" s="4"/>
-      <c r="D106" s="4"/>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A107" s="4"/>
-      <c r="B107" s="4"/>
-      <c r="C107" s="4"/>
-      <c r="D107" s="4"/>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A108" s="4"/>
-      <c r="B108" s="4"/>
-      <c r="C108" s="4"/>
-      <c r="D108" s="4"/>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A109" s="4"/>
-      <c r="B109" s="4"/>
-      <c r="C109" s="4"/>
-      <c r="D109" s="4"/>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A110" s="4"/>
-      <c r="B110" s="4"/>
-      <c r="C110" s="4"/>
-      <c r="D110" s="4"/>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A111" s="4"/>
-      <c r="B111" s="4"/>
-      <c r="C111" s="4"/>
-      <c r="D111" s="4"/>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A112" s="4"/>
-      <c r="B112" s="4"/>
-      <c r="C112" s="4"/>
-      <c r="D112" s="4"/>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A113" s="4"/>
-      <c r="B113" s="4"/>
-      <c r="C113" s="4"/>
-      <c r="D113" s="4"/>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A114" s="4"/>
-      <c r="B114" s="4"/>
-      <c r="C114" s="4"/>
-      <c r="D114" s="4"/>
-    </row>
     <row r="115" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A115" s="39" t="s">
+      <c r="A115" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="B115" s="40" t="s">
+      <c r="B115" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="C115" s="41" t="s">
+      <c r="C115" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="D115" s="40">
+      <c r="D115" s="38">
         <v>256</v>
       </c>
     </row>
@@ -9644,7 +9513,7 @@
       </c>
     </row>
     <row r="117" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A117" s="42">
+      <c r="A117" s="40">
         <v>4</v>
       </c>
       <c r="B117" s="3">
@@ -9661,24 +9530,24 @@
       </c>
     </row>
     <row r="118" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A118" s="43">
+      <c r="A118" s="41">
         <v>8</v>
       </c>
-      <c r="B118" s="44">
+      <c r="B118" s="42">
         <f>Datos!H71</f>
         <v>46440</v>
       </c>
-      <c r="C118" s="44">
+      <c r="C118" s="42">
         <f>Datos!H72</f>
         <v>41281</v>
       </c>
-      <c r="D118" s="44">
+      <c r="D118" s="42">
         <f>Datos!H73</f>
         <v>41281</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A119" s="42">
+      <c r="A119" s="40">
         <v>16</v>
       </c>
       <c r="B119" s="3">
@@ -9694,83 +9563,17 @@
         <v>41281</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A120" s="4"/>
-      <c r="B120" s="4"/>
-      <c r="C120" s="4"/>
-      <c r="D120" s="4"/>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A121" s="4"/>
-      <c r="B121" s="4"/>
-      <c r="C121" s="4"/>
-      <c r="D121" s="4"/>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A122" s="4"/>
-      <c r="B122" s="4"/>
-      <c r="C122" s="4"/>
-      <c r="D122" s="4"/>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A123" s="4"/>
-      <c r="B123" s="4"/>
-      <c r="C123" s="4"/>
-      <c r="D123" s="4"/>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A124" s="4"/>
-      <c r="B124" s="4"/>
-      <c r="C124" s="4"/>
-      <c r="D124" s="4"/>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A125" s="4"/>
-      <c r="B125" s="4"/>
-      <c r="C125" s="4"/>
-      <c r="D125" s="4"/>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A126" s="4"/>
-      <c r="B126" s="4"/>
-      <c r="C126" s="4"/>
-      <c r="D126" s="4"/>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A127" s="4"/>
-      <c r="B127" s="4"/>
-      <c r="C127" s="4"/>
-      <c r="D127" s="4"/>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A128" s="4"/>
-      <c r="B128" s="4"/>
-      <c r="C128" s="4"/>
-      <c r="D128" s="4"/>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A129" s="4"/>
-      <c r="B129" s="4"/>
-      <c r="C129" s="4"/>
-      <c r="D129" s="4"/>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A130" s="4"/>
-      <c r="B130" s="4"/>
-      <c r="C130" s="4"/>
-      <c r="D130" s="4"/>
-    </row>
     <row r="131" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A131" s="39" t="s">
+      <c r="A131" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="B131" s="40" t="s">
+      <c r="B131" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="C131" s="41" t="s">
+      <c r="C131" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="D131" s="40">
+      <c r="D131" s="38">
         <v>1024</v>
       </c>
     </row>
@@ -9789,7 +9592,7 @@
       </c>
     </row>
     <row r="133" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A133" s="42">
+      <c r="A133" s="40">
         <v>4</v>
       </c>
       <c r="B133" s="3">
@@ -9806,24 +9609,24 @@
       </c>
     </row>
     <row r="134" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A134" s="43">
+      <c r="A134" s="41">
         <v>8</v>
       </c>
-      <c r="B134" s="44">
+      <c r="B134" s="42">
         <f>Datos!H80</f>
         <v>11610</v>
       </c>
-      <c r="C134" s="44">
+      <c r="C134" s="42">
         <f>Datos!H81</f>
         <v>10321</v>
       </c>
-      <c r="D134" s="44">
+      <c r="D134" s="42">
         <f>Datos!H82</f>
         <v>10321</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A135" s="42">
+      <c r="A135" s="40">
         <v>16</v>
       </c>
       <c r="B135" s="3">
